--- a/paper_monitor_system/journal_list.xlsx
+++ b/paper_monitor_system/journal_list.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="Rb4431fad23d14d01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rde9dc34d3ca0410b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R1efef2785a9342b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="Rccb5612cd17947b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="R6cc4675f69ab4775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rc4ef36ec31a447dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R1e190e25d4344679"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="R7ae301b813cd4070"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -28,12 +28,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -48,7 +53,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -77,6 +82,10 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -352,17 +361,17 @@
       <x:c r="F2" s="10" t="str"/>
       <x:c r="G2" s="10" t="str"/>
       <x:c r="H2" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/applied-soft-computing/articles-in-press</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str"/>
       <x:c r="K2" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L2" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -384,17 +393,17 @@
       <x:c r="F3" s="10" t="str"/>
       <x:c r="G3" s="10" t="str"/>
       <x:c r="H3" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-industrial-engineering/articles-in-press</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str"/>
       <x:c r="K3" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -416,17 +425,17 @@
       <x:c r="F4" s="10" t="str"/>
       <x:c r="G4" s="10" t="str"/>
       <x:c r="H4" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-operations-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str"/>
       <x:c r="K4" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L4" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -448,17 +457,17 @@
       <x:c r="F5" s="10" t="str"/>
       <x:c r="G5" s="10" t="str"/>
       <x:c r="H5" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/decision-support-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str"/>
       <x:c r="K5" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -480,17 +489,17 @@
       <x:c r="F6" s="10" t="str"/>
       <x:c r="G6" s="10" t="str"/>
       <x:c r="H6" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/european-journal-of-operational-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str"/>
       <x:c r="K6" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -512,17 +521,17 @@
       <x:c r="F7" s="10" t="str"/>
       <x:c r="G7" s="10" t="str"/>
       <x:c r="H7" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/expert-systems-with-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str"/>
       <x:c r="K7" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -544,17 +553,17 @@
       <x:c r="F8" s="10" t="str"/>
       <x:c r="G8" s="10" t="str"/>
       <x:c r="H8" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/fuzzy-sets-and-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str"/>
       <x:c r="K8" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -576,17 +585,17 @@
       <x:c r="F9" s="10" t="str"/>
       <x:c r="G9" s="10" t="str"/>
       <x:c r="H9" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-fusion/articles-in-press</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str"/>
       <x:c r="K9" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -608,17 +617,17 @@
       <x:c r="F10" s="10" t="str"/>
       <x:c r="G10" s="10" t="str"/>
       <x:c r="H10" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-sciences/articles-in-press</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str"/>
       <x:c r="K10" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -640,17 +649,17 @@
       <x:c r="F11" s="10" t="str"/>
       <x:c r="G11" s="10" t="str"/>
       <x:c r="H11" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-approximate-reasoning/articles-in-press</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str"/>
       <x:c r="K11" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -672,17 +681,17 @@
       <x:c r="F12" s="10" t="str"/>
       <x:c r="G12" s="10" t="str"/>
       <x:c r="H12" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-production-economics/articles-in-press</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str"/>
       <x:c r="K12" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L12" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -704,17 +713,17 @@
       <x:c r="F13" s="10" t="str"/>
       <x:c r="G13" s="10" t="str"/>
       <x:c r="H13" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/knowledge-based-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str"/>
       <x:c r="K13" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L13" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -736,17 +745,17 @@
       <x:c r="F14" s="10" t="str"/>
       <x:c r="G14" s="10" t="str"/>
       <x:c r="H14" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/omega/articles-in-press</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str"/>
       <x:c r="K14" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L14" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -768,17 +777,17 @@
       <x:c r="F15" s="10" t="str"/>
       <x:c r="G15" s="10" t="str"/>
       <x:c r="H15" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/engineering-applications-of-artificial-intelligence/articles-in-press</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str"/>
       <x:c r="K15" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L15" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -800,17 +809,17 @@
       <x:c r="F16" s="10" t="str"/>
       <x:c r="G16" s="10" t="str"/>
       <x:c r="H16" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering/articles-in-press</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str"/>
       <x:c r="K16" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L16" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -832,17 +841,17 @@
       <x:c r="F17" s="10" t="str"/>
       <x:c r="G17" s="10" t="str"/>
       <x:c r="H17" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str"/>
       <x:c r="K17" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L17" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -864,17 +873,17 @@
       <x:c r="F18" s="10" t="str"/>
       <x:c r="G18" s="10" t="str"/>
       <x:c r="H18" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-forecasting/articles-in-press</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str"/>
       <x:c r="K18" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L18" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -896,17 +905,17 @@
       <x:c r="F19" s="10" t="str"/>
       <x:c r="G19" s="10" t="str"/>
       <x:c r="H19" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-and-management/articles-in-press</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str"/>
       <x:c r="K19" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L19" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -928,17 +937,17 @@
       <x:c r="F20" s="10" t="str"/>
       <x:c r="G20" s="10" t="str"/>
       <x:c r="H20" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str"/>
       <x:c r="K20" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L20" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -960,17 +969,17 @@
       <x:c r="F21" s="10" t="str"/>
       <x:c r="G21" s="10" t="str"/>
       <x:c r="H21" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/artificial-intelligence/articles-in-press</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str"/>
       <x:c r="K21" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L21" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -992,17 +1001,17 @@
       <x:c r="F22" s="10" t="str"/>
       <x:c r="G22" s="10" t="str"/>
       <x:c r="H22" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition/articles-in-press</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str"/>
       <x:c r="K22" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L22" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1024,17 +1033,17 @@
       <x:c r="F23" s="10" t="str"/>
       <x:c r="G23" s="10" t="str"/>
       <x:c r="H23" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition-letters/articles-in-press</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str"/>
       <x:c r="K23" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L23" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1056,17 +1065,17 @@
       <x:c r="F24" s="10" t="str"/>
       <x:c r="G24" s="10" t="str"/>
       <x:c r="H24" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/neurocomputing/articles-in-press</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str"/>
       <x:c r="K24" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L24" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1088,17 +1097,17 @@
       <x:c r="F25" s="10" t="str"/>
       <x:c r="G25" s="10" t="str"/>
       <x:c r="H25" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/physica-a-statistical-mechanics-and-its-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str"/>
       <x:c r="K25" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L25" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1120,17 +1129,17 @@
       <x:c r="F26" s="10" t="str"/>
       <x:c r="G26" s="10" t="str"/>
       <x:c r="H26" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety/articles-in-press</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str"/>
       <x:c r="K26" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L26" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1152,17 +1161,17 @@
       <x:c r="F27" s="10" t="str"/>
       <x:c r="G27" s="10" t="str"/>
       <x:c r="H27" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-biomedical-informatics/articles-in-press</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str"/>
       <x:c r="K27" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L27" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1182,17 +1191,17 @@
       <x:c r="F28" s="10" t="str"/>
       <x:c r="G28" s="10" t="str"/>
       <x:c r="H28" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/ai-open/articles-in-press</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str"/>
       <x:c r="K28" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L28" s="10" t="str">
-        <x:v>Online-only journal; current publisher page lists Online ISSN only.; Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1214,17 +1223,17 @@
       <x:c r="F29" s="10" t="str"/>
       <x:c r="G29" s="10" t="str"/>
       <x:c r="H29" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/neural-networks/articles-in-press</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str"/>
       <x:c r="K29" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L29" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1246,17 +1255,17 @@
       <x:c r="F30" s="10" t="str"/>
       <x:c r="G30" s="10" t="str"/>
       <x:c r="H30" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/advanced-engineering-informatics</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str"/>
       <x:c r="K30" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L30" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1278,17 +1287,17 @@
       <x:c r="F31" s="10" t="str"/>
       <x:c r="G31" s="10" t="str"/>
       <x:c r="H31" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-in-industry/articles-in-press</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str"/>
       <x:c r="K31" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L31" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1310,17 +1319,17 @@
       <x:c r="F32" s="10" t="str"/>
       <x:c r="G32" s="10" t="str"/>
       <x:c r="H32" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/technological-forecasting-and-social-change/articles-in-press</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str"/>
       <x:c r="K32" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L32" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1342,17 +1351,17 @@
       <x:c r="F33" s="10" t="str"/>
       <x:c r="G33" s="10" t="str"/>
       <x:c r="H33" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-retailing-and-consumer-services/articles-in-press</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str"/>
       <x:c r="K33" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L33" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1376,17 +1385,17 @@
       </x:c>
       <x:c r="G34" s="10" t="str"/>
       <x:c r="H34" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-b-methodological/articles-in-press</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str"/>
       <x:c r="K34" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L34" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1410,17 +1419,17 @@
       </x:c>
       <x:c r="G35" s="10" t="str"/>
       <x:c r="H35" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-d-transport-and-environment</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str"/>
       <x:c r="K35" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L35" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1444,17 +1453,17 @@
       </x:c>
       <x:c r="G36" s="10" t="str"/>
       <x:c r="H36" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-e-logistics-and-transportation-review</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str"/>
       <x:c r="K36" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L36" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1478,17 +1487,17 @@
       </x:c>
       <x:c r="G37" s="10" t="str"/>
       <x:c r="H37" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-processing-and-management/articles-in-press</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str"/>
       <x:c r="K37" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L37" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1510,17 +1519,17 @@
       <x:c r="F38" s="10" t="str"/>
       <x:c r="G38" s="10" t="str"/>
       <x:c r="H38" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/euro-journal-on-decision-processes/articles-in-press</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str"/>
       <x:c r="K38" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L38" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -1542,17 +1551,17 @@
       <x:c r="F39" s="10" t="str"/>
       <x:c r="G39" s="10" t="str"/>
       <x:c r="H39" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management/latest</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str"/>
       <x:c r="K39" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L39" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -1574,17 +1583,17 @@
       <x:c r="F40" s="10" t="str"/>
       <x:c r="G40" s="10" t="str"/>
       <x:c r="H40" s="10" t="str">
-        <x:v>sciencedirect_page</x:v>
+        <x:v>elsevier_incremental</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/annals-of-tourism-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str"/>
       <x:c r="K40" s="10" t="str">
-        <x:v>rss+crossref</x:v>
+        <x:v>direct-rss+crossref-indexed+pending</x:v>
       </x:c>
       <x:c r="L40" s="10" t="str">
-        <x:v>Page first; auto-discover ScienceDirect RSS when exposed; Crossref only as fallback.</x:v>
+        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -1606,17 +1615,17 @@
       <x:c r="F41" s="10" t="str"/>
       <x:c r="G41" s="10" t="str"/>
       <x:c r="H41" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I41" s="10" t="str">
         <x:v>http://link.springer.com/journal/10479/articles</x:v>
       </x:c>
       <x:c r="J41" s="10" t="str"/>
       <x:c r="K41" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L41" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -1638,17 +1647,17 @@
       <x:c r="F42" s="10" t="str"/>
       <x:c r="G42" s="10" t="str"/>
       <x:c r="H42" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str">
         <x:v>http://link.springer.com/journal/10700/articles</x:v>
       </x:c>
       <x:c r="J42" s="10" t="str"/>
       <x:c r="K42" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L42" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -1670,17 +1679,17 @@
       <x:c r="F43" s="10" t="str"/>
       <x:c r="G43" s="10" t="str"/>
       <x:c r="H43" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str">
         <x:v>http://link.springer.com/journal/10726/articles</x:v>
       </x:c>
       <x:c r="J43" s="10" t="str"/>
       <x:c r="K43" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L43" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -1702,17 +1711,17 @@
       <x:c r="F44" s="10" t="str"/>
       <x:c r="G44" s="10" t="str"/>
       <x:c r="H44" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I44" s="10" t="str">
         <x:v>http://link.springer.com/journal/500/articles</x:v>
       </x:c>
       <x:c r="J44" s="10" t="str"/>
       <x:c r="K44" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L44" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -1734,17 +1743,17 @@
       <x:c r="F45" s="10" t="str"/>
       <x:c r="G45" s="10" t="str"/>
       <x:c r="H45" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str">
         <x:v>http://link.springer.com/journal/13042/articles</x:v>
       </x:c>
       <x:c r="J45" s="10" t="str"/>
       <x:c r="K45" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L45" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -1766,17 +1775,17 @@
       <x:c r="F46" s="10" t="str"/>
       <x:c r="G46" s="10" t="str"/>
       <x:c r="H46" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I46" s="10" t="str">
         <x:v>http://link.springer.com/journal/10115/articles</x:v>
       </x:c>
       <x:c r="J46" s="10" t="str"/>
       <x:c r="K46" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L46" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1798,17 +1807,17 @@
       <x:c r="F47" s="10" t="str"/>
       <x:c r="G47" s="10" t="str"/>
       <x:c r="H47" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I47" s="10" t="str">
         <x:v>http://link.springer.com/journal/521/articles</x:v>
       </x:c>
       <x:c r="J47" s="10" t="str"/>
       <x:c r="K47" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L47" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -1830,17 +1839,17 @@
       <x:c r="F48" s="10" t="str"/>
       <x:c r="G48" s="10" t="str"/>
       <x:c r="H48" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I48" s="10" t="str">
         <x:v>http://link.springer.com/journal/10489/articles</x:v>
       </x:c>
       <x:c r="J48" s="10" t="str"/>
       <x:c r="K48" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L48" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1862,17 +1871,17 @@
       <x:c r="F49" s="10" t="str"/>
       <x:c r="G49" s="10" t="str"/>
       <x:c r="H49" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I49" s="10" t="str">
         <x:v>http://link.springer.com/journal/12559/articles</x:v>
       </x:c>
       <x:c r="J49" s="10" t="str"/>
       <x:c r="K49" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L49" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1896,17 +1905,17 @@
       </x:c>
       <x:c r="G50" s="10" t="str"/>
       <x:c r="H50" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I50" s="10" t="str">
         <x:v>http://link.springer.com/journal/40747/articles</x:v>
       </x:c>
       <x:c r="J50" s="10" t="str"/>
       <x:c r="K50" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L50" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -1928,17 +1937,17 @@
       <x:c r="F51" s="10" t="str"/>
       <x:c r="G51" s="10" t="str"/>
       <x:c r="H51" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I51" s="10" t="str">
         <x:v>http://link.springer.com/journal/40815/articles</x:v>
       </x:c>
       <x:c r="J51" s="10" t="str"/>
       <x:c r="K51" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L51" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -1960,17 +1969,17 @@
       <x:c r="F52" s="10" t="str"/>
       <x:c r="G52" s="10" t="str"/>
       <x:c r="H52" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I52" s="10" t="str">
         <x:v>http://link.springer.com/journal/291/articles</x:v>
       </x:c>
       <x:c r="J52" s="10" t="str"/>
       <x:c r="K52" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L52" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -1992,17 +2001,17 @@
       <x:c r="F53" s="10" t="str"/>
       <x:c r="G53" s="10" t="str"/>
       <x:c r="H53" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I53" s="10" t="str">
         <x:v>https://link.springer.com/journal/10462/articles</x:v>
       </x:c>
       <x:c r="J53" s="10" t="str"/>
       <x:c r="K53" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L53" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -2026,17 +2035,17 @@
       </x:c>
       <x:c r="G54" s="10" t="str"/>
       <x:c r="H54" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str">
         <x:v>https://link.springer.com/journal/42524/articles</x:v>
       </x:c>
       <x:c r="J54" s="10" t="str"/>
       <x:c r="K54" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L54" s="10" t="str">
-        <x:v>Renamed from Frontiers of Engineering Management in January 2026. Former pISSN/eISSN: 2095-7513 / 2096-0255. Current ISSNs are used for live monitoring.; Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>Renamed from Frontiers of Engineering Management in January 2026. Former pISSN/eISSN: 2095-7513 / 2096-0255. Current ISSNs are used for live monitoring. LOCAL V2: batch Meta API first; per-journal API/Online First/Crossref fallback.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -2058,17 +2067,17 @@
       <x:c r="F55" s="10" t="str"/>
       <x:c r="G55" s="10" t="str"/>
       <x:c r="H55" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str">
         <x:v>http://link.springer.com/journal/11518/articles</x:v>
       </x:c>
       <x:c r="J55" s="10" t="str"/>
       <x:c r="K55" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L55" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -2090,17 +2099,17 @@
       <x:c r="F56" s="10" t="str"/>
       <x:c r="G56" s="10" t="str"/>
       <x:c r="H56" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I56" s="10" t="str">
         <x:v>http://link.springer.com/journal/11424/articles</x:v>
       </x:c>
       <x:c r="J56" s="10" t="str"/>
       <x:c r="K56" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L56" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -2124,17 +2133,17 @@
       </x:c>
       <x:c r="G57" s="10" t="str"/>
       <x:c r="H57" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I57" s="10" t="str">
         <x:v>http://link.springer.com/journal/10618/articles</x:v>
       </x:c>
       <x:c r="J57" s="10" t="str"/>
       <x:c r="K57" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L57" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -2156,17 +2165,17 @@
       <x:c r="F58" s="10" t="str"/>
       <x:c r="G58" s="10" t="str"/>
       <x:c r="H58" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I58" s="10" t="str">
         <x:v>https://link.springer.com/journal/13278/articles</x:v>
       </x:c>
       <x:c r="J58" s="10" t="str"/>
       <x:c r="K58" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L58" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -2188,17 +2197,17 @@
       <x:c r="F59" s="10" t="str"/>
       <x:c r="G59" s="10" t="str"/>
       <x:c r="H59" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I59" s="10" t="str">
         <x:v>http://link.springer.com/journal/10729/articles</x:v>
       </x:c>
       <x:c r="J59" s="10" t="str"/>
       <x:c r="K59" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L59" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -2220,17 +2229,17 @@
       <x:c r="F60" s="10" t="str"/>
       <x:c r="G60" s="10" t="str"/>
       <x:c r="H60" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I60" s="10" t="str">
         <x:v>http://link.springer.com/journal/10660/articles</x:v>
       </x:c>
       <x:c r="J60" s="10" t="str"/>
       <x:c r="K60" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L60" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -2252,17 +2261,17 @@
       <x:c r="F61" s="10" t="str"/>
       <x:c r="G61" s="10" t="str"/>
       <x:c r="H61" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I61" s="10" t="str">
         <x:v>http://link.springer.com/journal/12351/articles</x:v>
       </x:c>
       <x:c r="J61" s="10" t="str"/>
       <x:c r="K61" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L61" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -2284,17 +2293,17 @@
       <x:c r="F62" s="10" t="str"/>
       <x:c r="G62" s="10" t="str"/>
       <x:c r="H62" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I62" s="10" t="str">
         <x:v>http://link.springer.com/journal/11750/articles</x:v>
       </x:c>
       <x:c r="J62" s="10" t="str"/>
       <x:c r="K62" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L62" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -2316,17 +2325,17 @@
       <x:c r="F63" s="10" t="str"/>
       <x:c r="G63" s="10" t="str"/>
       <x:c r="H63" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I63" s="10" t="str">
         <x:v>http://link.springer.com/journal/11238/articles</x:v>
       </x:c>
       <x:c r="J63" s="10" t="str"/>
       <x:c r="K63" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L63" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -2348,17 +2357,17 @@
       <x:c r="F64" s="10" t="str"/>
       <x:c r="G64" s="10" t="str"/>
       <x:c r="H64" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I64" s="10" t="str">
         <x:v>http://link.springer.com/journal/10100/articles</x:v>
       </x:c>
       <x:c r="J64" s="10" t="str"/>
       <x:c r="K64" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L64" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -2380,17 +2389,17 @@
       <x:c r="F65" s="10" t="str"/>
       <x:c r="G65" s="10" t="str"/>
       <x:c r="H65" s="10" t="str">
-        <x:v>springer_api</x:v>
+        <x:v>springer_batch_api</x:v>
       </x:c>
       <x:c r="I65" s="10" t="str">
         <x:v>https://www.springer.com/journal/44196</x:v>
       </x:c>
       <x:c r="J65" s="10" t="str"/>
       <x:c r="K65" s="10" t="str">
-        <x:v>online-first+crossref</x:v>
+        <x:v>per-journal-api+online-first+crossref</x:v>
       </x:c>
       <x:c r="L65" s="10" t="str">
-        <x:v>Springer Meta API first; Online First page second; Crossref fallback.</x:v>
+        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -2421,10 +2430,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K66" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L66" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -2455,10 +2464,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K67" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L67" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -2487,10 +2496,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K68" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L68" s="10" t="str">
-        <x:v>IEEE Xplore currently identifies 2329-924X as the Electronic ISSN.; Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -2521,10 +2530,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K69" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L69" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -2555,10 +2564,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K70" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L70" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -2589,10 +2598,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K71" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L71" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -2621,10 +2630,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K72" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L72" s="10" t="str">
-        <x:v>IEEE Xplore currently lists an Electronic ISSN only.; Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -2655,10 +2664,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K73" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L73" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -2689,10 +2698,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K74" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L74" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -2723,10 +2732,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K75" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L75" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -2757,10 +2766,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K76" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L76" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -2789,10 +2798,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K77" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L77" s="10" t="str">
-        <x:v>IEEE Xplore currently identifies 2332-7790 as the Electronic ISSN.; Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -2821,10 +2830,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K78" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L78" s="10" t="str">
-        <x:v>IEEE Xplore currently identifies 2327-4697 as the Electronic ISSN.; Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -2855,10 +2864,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K79" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L79" s="10" t="str">
-        <x:v>Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -2887,10 +2896,10 @@
         <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
       </x:c>
       <x:c r="K80" s="10" t="str">
-        <x:v>crossref</x:v>
+        <x:v>crossref-date-validation</x:v>
       </x:c>
       <x:c r="L80" s="10" t="str">
-        <x:v>IEEE Xplore currently identifies 2471-285X as the Electronic ISSN.; Shared combined Saved Search RSS (IEEETrans15); program fetches it once and maps entries back to the 15-journal whitelist.</x:v>
+        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2902,7 +2911,7 @@
       <x:formula1>"Elsevier,Springer Nature,IEEE"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="H2:H500">
-      <x:formula1>"sciencedirect_page,springer_api,ieee_saved_search_rss,auto"</x:formula1>
+      <x:formula1>"elsevier_incremental,springer_batch_api,ieee_saved_search_rss,auto"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2942,13 +2951,13 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="str">
-        <x:v>ScienceDirect strategy</x:v>
+        <x:v>Elsevier strategy</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>Page → discovered RSS → Crossref</x:v>
+        <x:v>Direct RSS (when configured) + Crossref index-date incremental discovery</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>Articles in Press is probed first; if absent, Latest / journal landing pages are checked.</x:v>
+        <x:v>ScienceDirect API/page scraping are disabled by default. Crossref-discovered records without published-online are retained as pending and rechecked.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2956,10 +2965,10 @@
         <x:v>Springer strategy</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>Meta API → Online First page → Crossref</x:v>
+        <x:v>Batch Meta API → per-journal Meta API → Online First → Crossref</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>onlineDate is authoritative when returned by the Springer Meta API.</x:v>
+        <x:v>A date-window Meta API query is attempted once and filtered locally to the 25-journal whitelist; onlineDate remains authoritative.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2967,10 +2976,21 @@
         <x:v>IEEE strategy</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>Combined Saved Search RSS → IEEE page/Crossref validation</x:v>
+        <x:v>Combined Saved Search RSS → publisher/Crossref date validation</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>RSS entry timestamps are not treated as online publication dates.</x:v>
+        <x:v>The exact IEEETrans15 feed is preserved; RSS timestamps are discovery-only and Virtual Journals/Compendia are removed by the whitelist.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>Pending policy</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>Crossref-discovered DOI without published-online → pending → recheck</x:v>
+      </x:c>
+      <x:c r="C6" s="10" t="str">
+        <x:v>Pending records remain in SQLite but are not exported to the public JSON until a real online date is available.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2987,10 +3007,10 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="12" t="str">
+      <x:c r="A1" s="15" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="15" t="str">
         <x:v>Instruction</x:v>
       </x:c>
     </x:row>
@@ -3007,7 +3027,7 @@
         <x:v>Mode</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>Elsevier uses sciencedirect_page; Springer uses springer_api; IEEE uses ieee_saved_search_rss.</x:v>
+        <x:v>Elsevier uses elsevier_incremental; Springer uses springer_batch_api; IEEE uses ieee_saved_search_rss.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3015,7 +3035,7 @@
         <x:v>Primary URL</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>Publisher journal page. ScienceDirect probes Articles in Press / Latest automatically.</x:v>
+        <x:v>Retained as a human/reference publisher URL. ScienceDirect page scraping is disabled by default in LOCAL V2 after local HTTP 403 results.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3023,7 +3043,7 @@
         <x:v>RSS URL</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>For IEEE all 15 rows intentionally share the same Saved Search RSS. The crawler deduplicates the URL and requests it only once.</x:v>
+        <x:v>Elsevier: optional direct feed URL if you have a stable RSS address; blank is allowed. IEEE: all 15 rows intentionally share the same IEEETrans15 Saved Search RSS and it is fetched once.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3031,31 +3051,39 @@
         <x:v>Fallback</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>Crossref supplements metadata/date validation. A Crossref fallback date never overwrites a higher-priority publisher date.</x:v>
+        <x:v>Elsevier uses Crossref index-date incremental discovery + pending. Springer uses per-journal API/Online First/Crossref when the batch API path fails. IEEE uses publisher/Crossref date validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
-        <x:v>IEEE filtering</x:v>
+        <x:v>Pending</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>The crawler still enforces the 15-journal whitelist, so Virtual Journals/Compendia that appear in the feed are discarded unless the underlying article maps to one of the monitored journals.</x:v>
+        <x:v>Crossref items without published-online are saved as pending in SQLite and rechecked later; pending rows are never shown on the public page.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
-        <x:v>Date policy</x:v>
+        <x:v>IEEE filtering</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>RSS pubDate is discovery time only. The displayed online date must come from a publisher page/API or Crossref published-online metadata.</x:v>
+        <x:v>The crawler enforces the 15-journal whitelist, so Virtual Journals/Compendia are discarded unless underlying metadata resolves to a monitored journal.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
+        <x:v>Date policy</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>RSS pubDate is discovery time only. The displayed online date must come from Springer onlineDate, publisher metadata, or Crossref published-online.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
         <x:v>Security</x:v>
       </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>API keys remain in GitHub Repository Secrets; they are never stored in this workbook.</x:v>
+      <x:c r="B10" s="10" t="str">
+        <x:v>API keys are stored only in local paper_monitor_system/.env, which is excluded by .gitignore. Do not put keys in this workbook or public web files.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/paper_monitor_system/journal_list.xlsx
+++ b/paper_monitor_system/journal_list.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="R6cc4675f69ab4775"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rc4ef36ec31a447dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R1e190e25d4344679"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="R7ae301b813cd4070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="Rc2e5e7179af843c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Ra5938cb21afa4bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R800a3e0b74d04e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="R822219bce9bb466c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -28,12 +28,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -53,7 +58,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -86,6 +91,17 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -302,6 +318,9 @@
     <x:col min="10" max="10" width="72" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="72" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -341,6 +360,15 @@
       <x:c r="L1" s="5" t="str">
         <x:v>Notes</x:v>
       </x:c>
+      <x:c r="M1" s="20" t="str">
+        <x:v>Crossref Member</x:v>
+      </x:c>
+      <x:c r="N1" s="20" t="str">
+        <x:v>Crossref Prefix</x:v>
+      </x:c>
+      <x:c r="O1" s="20" t="str">
+        <x:v>Crossref Group</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="n">
@@ -361,17 +389,26 @@
       <x:c r="F2" s="10" t="str"/>
       <x:c r="G2" s="10" t="str"/>
       <x:c r="H2" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/applied-soft-computing/articles-in-press</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str"/>
       <x:c r="K2" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L2" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M2" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -393,17 +430,26 @@
       <x:c r="F3" s="10" t="str"/>
       <x:c r="G3" s="10" t="str"/>
       <x:c r="H3" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-industrial-engineering/articles-in-press</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str"/>
       <x:c r="K3" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M3" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O3" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -425,17 +471,26 @@
       <x:c r="F4" s="10" t="str"/>
       <x:c r="G4" s="10" t="str"/>
       <x:c r="H4" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-operations-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str"/>
       <x:c r="K4" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L4" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M4" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N4" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O4" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -457,17 +512,26 @@
       <x:c r="F5" s="10" t="str"/>
       <x:c r="G5" s="10" t="str"/>
       <x:c r="H5" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/decision-support-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str"/>
       <x:c r="K5" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M5" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N5" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O5" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -489,17 +553,26 @@
       <x:c r="F6" s="10" t="str"/>
       <x:c r="G6" s="10" t="str"/>
       <x:c r="H6" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/european-journal-of-operational-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str"/>
       <x:c r="K6" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M6" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N6" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O6" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -521,17 +594,26 @@
       <x:c r="F7" s="10" t="str"/>
       <x:c r="G7" s="10" t="str"/>
       <x:c r="H7" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/expert-systems-with-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str"/>
       <x:c r="K7" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N7" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O7" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -553,17 +635,26 @@
       <x:c r="F8" s="10" t="str"/>
       <x:c r="G8" s="10" t="str"/>
       <x:c r="H8" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/fuzzy-sets-and-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str"/>
       <x:c r="K8" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N8" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O8" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -585,17 +676,26 @@
       <x:c r="F9" s="10" t="str"/>
       <x:c r="G9" s="10" t="str"/>
       <x:c r="H9" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-fusion/articles-in-press</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str"/>
       <x:c r="K9" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -617,17 +717,26 @@
       <x:c r="F10" s="10" t="str"/>
       <x:c r="G10" s="10" t="str"/>
       <x:c r="H10" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-sciences/articles-in-press</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str"/>
       <x:c r="K10" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M10" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N10" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O10" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -649,17 +758,26 @@
       <x:c r="F11" s="10" t="str"/>
       <x:c r="G11" s="10" t="str"/>
       <x:c r="H11" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-approximate-reasoning/articles-in-press</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str"/>
       <x:c r="K11" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N11" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O11" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -681,17 +799,26 @@
       <x:c r="F12" s="10" t="str"/>
       <x:c r="G12" s="10" t="str"/>
       <x:c r="H12" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-production-economics/articles-in-press</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str"/>
       <x:c r="K12" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L12" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M12" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N12" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O12" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -713,17 +840,26 @@
       <x:c r="F13" s="10" t="str"/>
       <x:c r="G13" s="10" t="str"/>
       <x:c r="H13" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/knowledge-based-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str"/>
       <x:c r="K13" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L13" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M13" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N13" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O13" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -745,17 +881,26 @@
       <x:c r="F14" s="10" t="str"/>
       <x:c r="G14" s="10" t="str"/>
       <x:c r="H14" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/omega/articles-in-press</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str"/>
       <x:c r="K14" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L14" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M14" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N14" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O14" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -777,17 +922,26 @@
       <x:c r="F15" s="10" t="str"/>
       <x:c r="G15" s="10" t="str"/>
       <x:c r="H15" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/engineering-applications-of-artificial-intelligence/articles-in-press</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str"/>
       <x:c r="K15" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L15" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M15" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N15" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O15" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -809,17 +963,26 @@
       <x:c r="F16" s="10" t="str"/>
       <x:c r="G16" s="10" t="str"/>
       <x:c r="H16" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering/articles-in-press</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str"/>
       <x:c r="K16" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L16" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M16" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N16" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O16" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -841,17 +1004,26 @@
       <x:c r="F17" s="10" t="str"/>
       <x:c r="G17" s="10" t="str"/>
       <x:c r="H17" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str"/>
       <x:c r="K17" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L17" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M17" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N17" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O17" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -873,17 +1045,26 @@
       <x:c r="F18" s="10" t="str"/>
       <x:c r="G18" s="10" t="str"/>
       <x:c r="H18" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-forecasting/articles-in-press</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str"/>
       <x:c r="K18" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L18" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M18" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N18" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O18" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -905,17 +1086,26 @@
       <x:c r="F19" s="10" t="str"/>
       <x:c r="G19" s="10" t="str"/>
       <x:c r="H19" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-and-management/articles-in-press</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str"/>
       <x:c r="K19" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L19" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M19" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N19" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O19" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -937,17 +1127,26 @@
       <x:c r="F20" s="10" t="str"/>
       <x:c r="G20" s="10" t="str"/>
       <x:c r="H20" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str"/>
       <x:c r="K20" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L20" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M20" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O20" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -969,17 +1168,26 @@
       <x:c r="F21" s="10" t="str"/>
       <x:c r="G21" s="10" t="str"/>
       <x:c r="H21" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/artificial-intelligence/articles-in-press</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str"/>
       <x:c r="K21" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L21" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M21" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O21" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1001,17 +1209,26 @@
       <x:c r="F22" s="10" t="str"/>
       <x:c r="G22" s="10" t="str"/>
       <x:c r="H22" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition/articles-in-press</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str"/>
       <x:c r="K22" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L22" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M22" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O22" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1033,17 +1250,26 @@
       <x:c r="F23" s="10" t="str"/>
       <x:c r="G23" s="10" t="str"/>
       <x:c r="H23" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition-letters/articles-in-press</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str"/>
       <x:c r="K23" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L23" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M23" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O23" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1065,17 +1291,26 @@
       <x:c r="F24" s="10" t="str"/>
       <x:c r="G24" s="10" t="str"/>
       <x:c r="H24" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/neurocomputing/articles-in-press</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str"/>
       <x:c r="K24" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L24" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M24" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N24" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O24" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1097,17 +1332,26 @@
       <x:c r="F25" s="10" t="str"/>
       <x:c r="G25" s="10" t="str"/>
       <x:c r="H25" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/physica-a-statistical-mechanics-and-its-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str"/>
       <x:c r="K25" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L25" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M25" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1129,17 +1373,26 @@
       <x:c r="F26" s="10" t="str"/>
       <x:c r="G26" s="10" t="str"/>
       <x:c r="H26" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety/articles-in-press</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str"/>
       <x:c r="K26" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L26" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M26" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O26" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1161,17 +1414,26 @@
       <x:c r="F27" s="10" t="str"/>
       <x:c r="G27" s="10" t="str"/>
       <x:c r="H27" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-biomedical-informatics/articles-in-press</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str"/>
       <x:c r="K27" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L27" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M27" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O27" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1191,17 +1453,26 @@
       <x:c r="F28" s="10" t="str"/>
       <x:c r="G28" s="10" t="str"/>
       <x:c r="H28" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/ai-open/articles-in-press</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str"/>
       <x:c r="K28" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L28" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M28" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O28" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1223,17 +1494,26 @@
       <x:c r="F29" s="10" t="str"/>
       <x:c r="G29" s="10" t="str"/>
       <x:c r="H29" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/neural-networks/articles-in-press</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str"/>
       <x:c r="K29" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L29" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M29" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O29" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1255,17 +1535,26 @@
       <x:c r="F30" s="10" t="str"/>
       <x:c r="G30" s="10" t="str"/>
       <x:c r="H30" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/advanced-engineering-informatics</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str"/>
       <x:c r="K30" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L30" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O30" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1287,17 +1576,26 @@
       <x:c r="F31" s="10" t="str"/>
       <x:c r="G31" s="10" t="str"/>
       <x:c r="H31" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-in-industry/articles-in-press</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str"/>
       <x:c r="K31" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L31" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M31" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1319,17 +1617,26 @@
       <x:c r="F32" s="10" t="str"/>
       <x:c r="G32" s="10" t="str"/>
       <x:c r="H32" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/technological-forecasting-and-social-change/articles-in-press</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str"/>
       <x:c r="K32" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L32" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1351,17 +1658,26 @@
       <x:c r="F33" s="10" t="str"/>
       <x:c r="G33" s="10" t="str"/>
       <x:c r="H33" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-retailing-and-consumer-services/articles-in-press</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str"/>
       <x:c r="K33" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L33" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M33" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O33" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1385,17 +1701,26 @@
       </x:c>
       <x:c r="G34" s="10" t="str"/>
       <x:c r="H34" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-b-methodological/articles-in-press</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str"/>
       <x:c r="K34" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L34" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M34" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O34" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1419,17 +1744,26 @@
       </x:c>
       <x:c r="G35" s="10" t="str"/>
       <x:c r="H35" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-d-transport-and-environment</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str"/>
       <x:c r="K35" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L35" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M35" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N35" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O35" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1453,17 +1787,26 @@
       </x:c>
       <x:c r="G36" s="10" t="str"/>
       <x:c r="H36" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-e-logistics-and-transportation-review</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str"/>
       <x:c r="K36" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L36" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M36" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O36" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1487,17 +1830,26 @@
       </x:c>
       <x:c r="G37" s="10" t="str"/>
       <x:c r="H37" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-processing-and-management/articles-in-press</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str"/>
       <x:c r="K37" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L37" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M37" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O37" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1519,17 +1871,26 @@
       <x:c r="F38" s="10" t="str"/>
       <x:c r="G38" s="10" t="str"/>
       <x:c r="H38" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/euro-journal-on-decision-processes/articles-in-press</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str"/>
       <x:c r="K38" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L38" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M38" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -1551,17 +1912,26 @@
       <x:c r="F39" s="10" t="str"/>
       <x:c r="G39" s="10" t="str"/>
       <x:c r="H39" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management/latest</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str"/>
       <x:c r="K39" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L39" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M39" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -1583,17 +1953,26 @@
       <x:c r="F40" s="10" t="str"/>
       <x:c r="G40" s="10" t="str"/>
       <x:c r="H40" s="10" t="str">
-        <x:v>elsevier_incremental</x:v>
+        <x:v>elsevier_member_batch</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/annals-of-tourism-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str"/>
       <x:c r="K40" s="10" t="str">
-        <x:v>direct-rss+crossref-indexed+pending</x:v>
+        <x:v>direct-rss+crossref-member-batch+pending</x:v>
       </x:c>
       <x:c r="L40" s="10" t="str">
-        <x:v>LOCAL V2: Crossref index-date incremental discovery is always active. If a stable direct RSS URL is entered in column J, it is merged as an additional discovery channel. ScienceDirect API/page scraping are disabled by default after local 401/403 tests.</x:v>
+        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+      </x:c>
+      <x:c r="M40" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>10.1016</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -1627,6 +2006,9 @@
       <x:c r="L41" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M41"/>
+      <x:c r="N41"/>
+      <x:c r="O41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="n">
@@ -1659,6 +2041,9 @@
       <x:c r="L42" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M42"/>
+      <x:c r="N42"/>
+      <x:c r="O42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="n">
@@ -1691,6 +2076,9 @@
       <x:c r="L43" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M43"/>
+      <x:c r="N43"/>
+      <x:c r="O43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="n">
@@ -1723,6 +2111,9 @@
       <x:c r="L44" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M44"/>
+      <x:c r="N44"/>
+      <x:c r="O44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="n">
@@ -1755,6 +2146,9 @@
       <x:c r="L45" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M45"/>
+      <x:c r="N45"/>
+      <x:c r="O45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="n">
@@ -1787,6 +2181,9 @@
       <x:c r="L46" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M46"/>
+      <x:c r="N46"/>
+      <x:c r="O46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="n">
@@ -1819,6 +2216,9 @@
       <x:c r="L47" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M47"/>
+      <x:c r="N47"/>
+      <x:c r="O47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="n">
@@ -1851,6 +2251,9 @@
       <x:c r="L48" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M48"/>
+      <x:c r="N48"/>
+      <x:c r="O48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="n">
@@ -1883,6 +2286,9 @@
       <x:c r="L49" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M49"/>
+      <x:c r="N49"/>
+      <x:c r="O49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="n">
@@ -1917,6 +2323,9 @@
       <x:c r="L50" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M50"/>
+      <x:c r="N50"/>
+      <x:c r="O50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="n">
@@ -1949,6 +2358,9 @@
       <x:c r="L51" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M51"/>
+      <x:c r="N51"/>
+      <x:c r="O51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="n">
@@ -1981,6 +2393,9 @@
       <x:c r="L52" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M52"/>
+      <x:c r="N52"/>
+      <x:c r="O52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="n">
@@ -2013,6 +2428,9 @@
       <x:c r="L53" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M53"/>
+      <x:c r="N53"/>
+      <x:c r="O53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="n">
@@ -2047,6 +2465,9 @@
       <x:c r="L54" s="10" t="str">
         <x:v>Renamed from Frontiers of Engineering Management in January 2026. Former pISSN/eISSN: 2095-7513 / 2096-0255. Current ISSNs are used for live monitoring. LOCAL V2: batch Meta API first; per-journal API/Online First/Crossref fallback.</x:v>
       </x:c>
+      <x:c r="M54"/>
+      <x:c r="N54"/>
+      <x:c r="O54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="n">
@@ -2079,6 +2500,9 @@
       <x:c r="L55" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M55"/>
+      <x:c r="N55"/>
+      <x:c r="O55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="10" t="n">
@@ -2111,6 +2535,9 @@
       <x:c r="L56" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M56"/>
+      <x:c r="N56"/>
+      <x:c r="O56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="10" t="n">
@@ -2145,6 +2572,9 @@
       <x:c r="L57" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M57"/>
+      <x:c r="N57"/>
+      <x:c r="O57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="10" t="n">
@@ -2177,6 +2607,9 @@
       <x:c r="L58" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M58"/>
+      <x:c r="N58"/>
+      <x:c r="O58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="10" t="n">
@@ -2209,6 +2642,9 @@
       <x:c r="L59" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M59"/>
+      <x:c r="N59"/>
+      <x:c r="O59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="n">
@@ -2241,6 +2677,9 @@
       <x:c r="L60" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M60"/>
+      <x:c r="N60"/>
+      <x:c r="O60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="n">
@@ -2273,6 +2712,9 @@
       <x:c r="L61" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M61"/>
+      <x:c r="N61"/>
+      <x:c r="O61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="n">
@@ -2305,6 +2747,9 @@
       <x:c r="L62" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M62"/>
+      <x:c r="N62"/>
+      <x:c r="O62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="n">
@@ -2337,6 +2782,9 @@
       <x:c r="L63" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M63"/>
+      <x:c r="N63"/>
+      <x:c r="O63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="n">
@@ -2369,6 +2817,9 @@
       <x:c r="L64" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M64"/>
+      <x:c r="N64"/>
+      <x:c r="O64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="n">
@@ -2401,6 +2852,9 @@
       <x:c r="L65" s="10" t="str">
         <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
       </x:c>
+      <x:c r="M65"/>
+      <x:c r="N65"/>
+      <x:c r="O65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="n">
@@ -2435,6 +2889,9 @@
       <x:c r="L66" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M66"/>
+      <x:c r="N66"/>
+      <x:c r="O66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="n">
@@ -2469,6 +2926,9 @@
       <x:c r="L67" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M67"/>
+      <x:c r="N67"/>
+      <x:c r="O67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="n">
@@ -2501,6 +2961,9 @@
       <x:c r="L68" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M68"/>
+      <x:c r="N68"/>
+      <x:c r="O68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="n">
@@ -2535,6 +2998,9 @@
       <x:c r="L69" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M69"/>
+      <x:c r="N69"/>
+      <x:c r="O69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="n">
@@ -2569,6 +3035,9 @@
       <x:c r="L70" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M70"/>
+      <x:c r="N70"/>
+      <x:c r="O70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="n">
@@ -2603,6 +3072,9 @@
       <x:c r="L71" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M71"/>
+      <x:c r="N71"/>
+      <x:c r="O71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10" t="n">
@@ -2635,6 +3107,9 @@
       <x:c r="L72" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M72"/>
+      <x:c r="N72"/>
+      <x:c r="O72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10" t="n">
@@ -2669,6 +3144,9 @@
       <x:c r="L73" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M73"/>
+      <x:c r="N73"/>
+      <x:c r="O73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="n">
@@ -2703,6 +3181,9 @@
       <x:c r="L74" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M74"/>
+      <x:c r="N74"/>
+      <x:c r="O74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="n">
@@ -2737,6 +3218,9 @@
       <x:c r="L75" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M75"/>
+      <x:c r="N75"/>
+      <x:c r="O75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="n">
@@ -2771,6 +3255,9 @@
       <x:c r="L76" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M76"/>
+      <x:c r="N76"/>
+      <x:c r="O76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="n">
@@ -2803,6 +3290,9 @@
       <x:c r="L77" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M77"/>
+      <x:c r="N77"/>
+      <x:c r="O77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="n">
@@ -2835,6 +3325,9 @@
       <x:c r="L78" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M78"/>
+      <x:c r="N78"/>
+      <x:c r="O78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="n">
@@ -2869,6 +3362,9 @@
       <x:c r="L79" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M79"/>
+      <x:c r="N79"/>
+      <x:c r="O79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="n">
@@ -2901,6 +3397,9 @@
       <x:c r="L80" s="10" t="str">
         <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
       </x:c>
+      <x:c r="M80"/>
+      <x:c r="N80"/>
+      <x:c r="O80"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
@@ -2984,13 +3483,46 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
-        <x:v>Pending policy</x:v>
+        <x:v>LOCAL V3 build</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>Crossref-discovered DOI without published-online → pending → recheck</x:v>
+        <x:v>LOCAL-2026.08.19-V3</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>Pending records remain in SQLite but are not exported to the public JSON until a real online date is available.</x:v>
+        <x:v>Optimized local-only collector.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="10" t="str">
+        <x:v>Elsevier strategy</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>Crossref member 78 + prefix 10.1016 → local whitelist</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>Created-date two-day batch; optional direct RSS supplement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="10" t="str">
+        <x:v>Pending strategy</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>DOI-only delayed recheck</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>No immediate same-run recheck; default minimum 20 hours between checks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
+        <x:v>Daily window</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>2 calendar dates</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>OVERLAP_DAYS=1 and CROSSREF_DISCOVERY_DAYS=2.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3080,10 +3612,50 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
-        <x:v>Security</x:v>
+        <x:v>LOCAL V3 Elsevier</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>API keys are stored only in local paper_monitor_system/.env, which is excluded by .gitignore. Do not put keys in this workbook or public web files.</x:v>
+        <x:v>All 39 Elsevier journals use Crossref Member 78 + prefix 10.1016 as one publisher-level batch, then local ISSN/title whitelist filtering.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="10" t="str">
+        <x:v>Crossref Member</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>Member ID used for publisher-level batch discovery. Default Elsevier BV = 78.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="10" t="str">
+        <x:v>Crossref Prefix</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>Optional DOI-owner prefix used to narrow the batch. Current Elsevier whitelist uses 10.1016.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
+        <x:v>Crossref Group</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>Human-readable batch group label; useful if a future journal needs a different member/prefix.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>Daily window</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>Default is yesterday..today (two calendar dates inclusive). Pending DOIs are rechecked separately by DOI only.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
+        <x:v>Performance</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>The V3 Elsevier path replaces 39–78 per-ISSN HTTP requests with one/few cursor-paged member-level requests.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/paper_monitor_system/journal_list.xlsx
+++ b/paper_monitor_system/journal_list.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="Rc2e5e7179af843c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Ra5938cb21afa4bad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R800a3e0b74d04e9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="R822219bce9bb466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="R76bb8ef040184ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rff48a18b368c4306"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R42c59937f2f04f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="R9d73779c8c0f42d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -389,24 +389,22 @@
       <x:c r="F2" s="10" t="str"/>
       <x:c r="G2" s="10" t="str"/>
       <x:c r="H2" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/applied-soft-computing/articles-in-press</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str"/>
       <x:c r="K2" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L2" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M2" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N2" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N2" t="str"/>
       <x:c r="O2" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -430,24 +428,22 @@
       <x:c r="F3" s="10" t="str"/>
       <x:c r="G3" s="10" t="str"/>
       <x:c r="H3" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-industrial-engineering/articles-in-press</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str"/>
       <x:c r="K3" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M3" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N3" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N3" t="str"/>
       <x:c r="O3" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -471,24 +467,22 @@
       <x:c r="F4" s="10" t="str"/>
       <x:c r="G4" s="10" t="str"/>
       <x:c r="H4" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-operations-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str"/>
       <x:c r="K4" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L4" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M4" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N4" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N4" t="str"/>
       <x:c r="O4" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -512,24 +506,22 @@
       <x:c r="F5" s="10" t="str"/>
       <x:c r="G5" s="10" t="str"/>
       <x:c r="H5" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/decision-support-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str"/>
       <x:c r="K5" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M5" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N5" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N5" t="str"/>
       <x:c r="O5" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -553,24 +545,22 @@
       <x:c r="F6" s="10" t="str"/>
       <x:c r="G6" s="10" t="str"/>
       <x:c r="H6" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/european-journal-of-operational-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str"/>
       <x:c r="K6" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M6" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N6" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N6" t="str"/>
       <x:c r="O6" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -594,24 +584,22 @@
       <x:c r="F7" s="10" t="str"/>
       <x:c r="G7" s="10" t="str"/>
       <x:c r="H7" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/expert-systems-with-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str"/>
       <x:c r="K7" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M7" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N7" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N7" t="str"/>
       <x:c r="O7" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -635,24 +623,22 @@
       <x:c r="F8" s="10" t="str"/>
       <x:c r="G8" s="10" t="str"/>
       <x:c r="H8" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/fuzzy-sets-and-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str"/>
       <x:c r="K8" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M8" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N8" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N8" t="str"/>
       <x:c r="O8" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -676,24 +662,22 @@
       <x:c r="F9" s="10" t="str"/>
       <x:c r="G9" s="10" t="str"/>
       <x:c r="H9" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-fusion/articles-in-press</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str"/>
       <x:c r="K9" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M9" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N9" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N9" t="str"/>
       <x:c r="O9" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -717,24 +701,22 @@
       <x:c r="F10" s="10" t="str"/>
       <x:c r="G10" s="10" t="str"/>
       <x:c r="H10" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-sciences/articles-in-press</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str"/>
       <x:c r="K10" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N10" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N10" t="str"/>
       <x:c r="O10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -758,24 +740,22 @@
       <x:c r="F11" s="10" t="str"/>
       <x:c r="G11" s="10" t="str"/>
       <x:c r="H11" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-approximate-reasoning/articles-in-press</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str"/>
       <x:c r="K11" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M11" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N11" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N11" t="str"/>
       <x:c r="O11" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -799,24 +779,22 @@
       <x:c r="F12" s="10" t="str"/>
       <x:c r="G12" s="10" t="str"/>
       <x:c r="H12" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-production-economics/articles-in-press</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str"/>
       <x:c r="K12" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L12" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M12" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N12" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N12" t="str"/>
       <x:c r="O12" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -840,24 +818,22 @@
       <x:c r="F13" s="10" t="str"/>
       <x:c r="G13" s="10" t="str"/>
       <x:c r="H13" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/knowledge-based-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str"/>
       <x:c r="K13" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L13" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M13" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N13" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N13" t="str"/>
       <x:c r="O13" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -881,24 +857,22 @@
       <x:c r="F14" s="10" t="str"/>
       <x:c r="G14" s="10" t="str"/>
       <x:c r="H14" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/omega/articles-in-press</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str"/>
       <x:c r="K14" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L14" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M14" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N14" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N14" t="str"/>
       <x:c r="O14" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -922,24 +896,22 @@
       <x:c r="F15" s="10" t="str"/>
       <x:c r="G15" s="10" t="str"/>
       <x:c r="H15" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/engineering-applications-of-artificial-intelligence/articles-in-press</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str"/>
       <x:c r="K15" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L15" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M15" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N15" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N15" t="str"/>
       <x:c r="O15" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -963,24 +935,22 @@
       <x:c r="F16" s="10" t="str"/>
       <x:c r="G16" s="10" t="str"/>
       <x:c r="H16" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering/articles-in-press</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str"/>
       <x:c r="K16" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L16" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M16" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N16" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N16" t="str"/>
       <x:c r="O16" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1004,24 +974,22 @@
       <x:c r="F17" s="10" t="str"/>
       <x:c r="G17" s="10" t="str"/>
       <x:c r="H17" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str"/>
       <x:c r="K17" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L17" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M17" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N17" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N17" t="str"/>
       <x:c r="O17" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1045,24 +1013,22 @@
       <x:c r="F18" s="10" t="str"/>
       <x:c r="G18" s="10" t="str"/>
       <x:c r="H18" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-forecasting/articles-in-press</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str"/>
       <x:c r="K18" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L18" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M18" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N18" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N18" t="str"/>
       <x:c r="O18" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1086,24 +1052,22 @@
       <x:c r="F19" s="10" t="str"/>
       <x:c r="G19" s="10" t="str"/>
       <x:c r="H19" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-and-management/articles-in-press</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str"/>
       <x:c r="K19" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L19" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M19" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N19" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N19" t="str"/>
       <x:c r="O19" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1127,24 +1091,22 @@
       <x:c r="F20" s="10" t="str"/>
       <x:c r="G20" s="10" t="str"/>
       <x:c r="H20" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str"/>
       <x:c r="K20" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L20" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M20" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N20" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N20" t="str"/>
       <x:c r="O20" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1168,24 +1130,22 @@
       <x:c r="F21" s="10" t="str"/>
       <x:c r="G21" s="10" t="str"/>
       <x:c r="H21" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/artificial-intelligence/articles-in-press</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str"/>
       <x:c r="K21" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L21" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M21" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N21" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N21" t="str"/>
       <x:c r="O21" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1209,24 +1169,22 @@
       <x:c r="F22" s="10" t="str"/>
       <x:c r="G22" s="10" t="str"/>
       <x:c r="H22" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition/articles-in-press</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str"/>
       <x:c r="K22" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L22" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M22" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N22" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N22" t="str"/>
       <x:c r="O22" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1250,24 +1208,22 @@
       <x:c r="F23" s="10" t="str"/>
       <x:c r="G23" s="10" t="str"/>
       <x:c r="H23" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition-letters/articles-in-press</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str"/>
       <x:c r="K23" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L23" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M23" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N23" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N23" t="str"/>
       <x:c r="O23" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1291,24 +1247,22 @@
       <x:c r="F24" s="10" t="str"/>
       <x:c r="G24" s="10" t="str"/>
       <x:c r="H24" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/neurocomputing/articles-in-press</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str"/>
       <x:c r="K24" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L24" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M24" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N24" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N24" t="str"/>
       <x:c r="O24" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1332,24 +1286,22 @@
       <x:c r="F25" s="10" t="str"/>
       <x:c r="G25" s="10" t="str"/>
       <x:c r="H25" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/physica-a-statistical-mechanics-and-its-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str"/>
       <x:c r="K25" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L25" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M25" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N25" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N25" t="str"/>
       <x:c r="O25" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1373,24 +1325,22 @@
       <x:c r="F26" s="10" t="str"/>
       <x:c r="G26" s="10" t="str"/>
       <x:c r="H26" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety/articles-in-press</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str"/>
       <x:c r="K26" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L26" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M26" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N26" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N26" t="str"/>
       <x:c r="O26" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1414,24 +1364,22 @@
       <x:c r="F27" s="10" t="str"/>
       <x:c r="G27" s="10" t="str"/>
       <x:c r="H27" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-biomedical-informatics/articles-in-press</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str"/>
       <x:c r="K27" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L27" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M27" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N27" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N27" t="str"/>
       <x:c r="O27" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1453,24 +1401,22 @@
       <x:c r="F28" s="10" t="str"/>
       <x:c r="G28" s="10" t="str"/>
       <x:c r="H28" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/ai-open/articles-in-press</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str"/>
       <x:c r="K28" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L28" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M28" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N28" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N28" t="str"/>
       <x:c r="O28" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1494,24 +1440,22 @@
       <x:c r="F29" s="10" t="str"/>
       <x:c r="G29" s="10" t="str"/>
       <x:c r="H29" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/neural-networks/articles-in-press</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str"/>
       <x:c r="K29" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L29" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M29" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N29" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N29" t="str"/>
       <x:c r="O29" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1535,24 +1479,22 @@
       <x:c r="F30" s="10" t="str"/>
       <x:c r="G30" s="10" t="str"/>
       <x:c r="H30" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/advanced-engineering-informatics</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str"/>
       <x:c r="K30" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L30" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M30" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N30" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N30" t="str"/>
       <x:c r="O30" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1576,24 +1518,22 @@
       <x:c r="F31" s="10" t="str"/>
       <x:c r="G31" s="10" t="str"/>
       <x:c r="H31" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-in-industry/articles-in-press</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str"/>
       <x:c r="K31" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L31" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M31" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N31" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N31" t="str"/>
       <x:c r="O31" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1617,24 +1557,22 @@
       <x:c r="F32" s="10" t="str"/>
       <x:c r="G32" s="10" t="str"/>
       <x:c r="H32" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/technological-forecasting-and-social-change/articles-in-press</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str"/>
       <x:c r="K32" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L32" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M32" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N32" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N32" t="str"/>
       <x:c r="O32" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1658,24 +1596,22 @@
       <x:c r="F33" s="10" t="str"/>
       <x:c r="G33" s="10" t="str"/>
       <x:c r="H33" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-retailing-and-consumer-services/articles-in-press</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str"/>
       <x:c r="K33" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L33" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M33" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N33" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N33" t="str"/>
       <x:c r="O33" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1701,24 +1637,22 @@
       </x:c>
       <x:c r="G34" s="10" t="str"/>
       <x:c r="H34" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-b-methodological/articles-in-press</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str"/>
       <x:c r="K34" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L34" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M34" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N34" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N34" t="str"/>
       <x:c r="O34" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1744,24 +1678,22 @@
       </x:c>
       <x:c r="G35" s="10" t="str"/>
       <x:c r="H35" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-d-transport-and-environment</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str"/>
       <x:c r="K35" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L35" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M35" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N35" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N35" t="str"/>
       <x:c r="O35" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1787,24 +1719,22 @@
       </x:c>
       <x:c r="G36" s="10" t="str"/>
       <x:c r="H36" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-e-logistics-and-transportation-review</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str"/>
       <x:c r="K36" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L36" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M36" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N36" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N36" t="str"/>
       <x:c r="O36" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1830,24 +1760,22 @@
       </x:c>
       <x:c r="G37" s="10" t="str"/>
       <x:c r="H37" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-processing-and-management/articles-in-press</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str"/>
       <x:c r="K37" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L37" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M37" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N37" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N37" t="str"/>
       <x:c r="O37" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1871,24 +1799,22 @@
       <x:c r="F38" s="10" t="str"/>
       <x:c r="G38" s="10" t="str"/>
       <x:c r="H38" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/euro-journal-on-decision-processes/articles-in-press</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str"/>
       <x:c r="K38" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L38" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M38" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N38" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N38" t="str"/>
       <x:c r="O38" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1912,24 +1838,22 @@
       <x:c r="F39" s="10" t="str"/>
       <x:c r="G39" s="10" t="str"/>
       <x:c r="H39" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management/latest</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str"/>
       <x:c r="K39" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L39" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M39" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N39" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N39" t="str"/>
       <x:c r="O39" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -1953,24 +1877,22 @@
       <x:c r="F40" s="10" t="str"/>
       <x:c r="G40" s="10" t="str"/>
       <x:c r="H40" s="10" t="str">
-        <x:v>elsevier_member_batch</x:v>
+        <x:v>elsevier_member_dual_batch</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/annals-of-tourism-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str"/>
       <x:c r="K40" s="10" t="str">
-        <x:v>direct-rss+crossref-member-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
       </x:c>
       <x:c r="L40" s="10" t="str">
-        <x:v>LOCAL V3: fast Crossref member-level created-date batch is the primary Elsevier discovery path. ScienceDirect API/page are optional and disabled by default. Stable direct RSS may be added as a supplement.</x:v>
+        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
       </x:c>
       <x:c r="M40" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N40" t="str">
-        <x:v>10.1016</x:v>
-      </x:c>
+      <x:c r="N40" t="str"/>
       <x:c r="O40" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
@@ -3483,13 +3405,13 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
-        <x:v>LOCAL V3 build</x:v>
+        <x:v>LOCAL V3.2 build</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>LOCAL-2026.08.19-V3</x:v>
+        <x:v>LOCAL-2026.08.19-V3.2</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>Optimized local-only collector.</x:v>
+        <x:v>Optimized local collector with dual Elsevier Crossref batch and IEEE RSS-date fallback.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3497,21 +3419,21 @@
         <x:v>Elsevier strategy</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>Crossref member 78 + prefix 10.1016 → local whitelist</x:v>
+        <x:v>Crossref member 78: online-date + update-date → local whitelist</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>Created-date two-day batch; optional direct RSS supplement.</x:v>
+        <x:v>No hard DOI prefix filter; direct RSS remains optional.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
-        <x:v>Pending strategy</x:v>
+        <x:v>IEEE strategy</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>DOI-only delayed recheck</x:v>
+        <x:v>Combined Saved Search RSS → Crossref/IEEE enrichment → RSS pubDate fallback</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>No immediate same-run recheck; default minimum 20 hours between checks.</x:v>
+        <x:v>RSS fallback is explicitly labelled and can later be replaced by a stronger publisher/Crossref date.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3612,10 +3534,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
-        <x:v>LOCAL V3 Elsevier</x:v>
+        <x:v>LOCAL V3.2 Elsevier</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>All 39 Elsevier journals use Crossref Member 78 + prefix 10.1016 as one publisher-level batch, then local ISSN/title whitelist filtering.</x:v>
+        <x:v>All 39 Elsevier journals use Crossref member 78 with two batch passes: published-online and update-date. No DOI-prefix hard filter is applied.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3623,7 +3545,7 @@
         <x:v>Crossref Member</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>Member ID used for publisher-level batch discovery. Default Elsevier BV = 78.</x:v>
+        <x:v>Publisher/member ID used for batch discovery. Elsevier BV = 78.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3631,23 +3553,23 @@
         <x:v>Crossref Prefix</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>Optional DOI-owner prefix used to narrow the batch. Current Elsevier whitelist uses 10.1016.</x:v>
+        <x:v>Optional informational/exception field. Blank for the standard V3.2 Elsevier group because final filtering is performed locally by ISSN/title.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="10" t="str">
-        <x:v>Crossref Group</x:v>
+        <x:v>IEEE RSS date</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>Human-readable batch group label; useful if a future journal needs a different member/prefix.</x:v>
+        <x:v>When IEEE page/Crossref does not yet expose a publication date, the Saved Search RSS pubDate may be used as a clearly labelled fallback date.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="10" t="str">
-        <x:v>Daily window</x:v>
+        <x:v>Pending</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>Default is yesterday..today (two calendar dates inclusive). Pending DOIs are rechecked separately by DOI only.</x:v>
+        <x:v>DOI-bearing records without a usable date remain pending and are rechecked later by DOI only.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3655,7 +3577,7 @@
         <x:v>Performance</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>The V3 Elsevier path replaces 39–78 per-ISSN HTTP requests with one/few cursor-paged member-level requests.</x:v>
+        <x:v>Elsevier avoids 39–78 per-ISSN calls; IEEE uses one combined feed; Springer remains batch-first.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/paper_monitor_system/journal_list.xlsx
+++ b/paper_monitor_system/journal_list.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="R76bb8ef040184ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rff48a18b368c4306"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R42c59937f2f04f8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="R9d73779c8c0f42d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="R8333d3755a7c4361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="R9669795b10394d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R6573af0fc7d041ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="Re7468899e7d145bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -389,17 +389,17 @@
       <x:c r="F2" s="10" t="str"/>
       <x:c r="G2" s="10" t="str"/>
       <x:c r="H2" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/applied-soft-computing/articles-in-press</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str"/>
       <x:c r="K2" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L2" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M2" t="n">
         <x:v>78</x:v>
@@ -428,17 +428,17 @@
       <x:c r="F3" s="10" t="str"/>
       <x:c r="G3" s="10" t="str"/>
       <x:c r="H3" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-industrial-engineering/articles-in-press</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str"/>
       <x:c r="K3" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M3" t="n">
         <x:v>78</x:v>
@@ -467,17 +467,17 @@
       <x:c r="F4" s="10" t="str"/>
       <x:c r="G4" s="10" t="str"/>
       <x:c r="H4" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-and-operations-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str"/>
       <x:c r="K4" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L4" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M4" t="n">
         <x:v>78</x:v>
@@ -506,17 +506,17 @@
       <x:c r="F5" s="10" t="str"/>
       <x:c r="G5" s="10" t="str"/>
       <x:c r="H5" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/decision-support-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str"/>
       <x:c r="K5" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M5" t="n">
         <x:v>78</x:v>
@@ -545,17 +545,17 @@
       <x:c r="F6" s="10" t="str"/>
       <x:c r="G6" s="10" t="str"/>
       <x:c r="H6" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/european-journal-of-operational-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str"/>
       <x:c r="K6" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M6" t="n">
         <x:v>78</x:v>
@@ -584,17 +584,17 @@
       <x:c r="F7" s="10" t="str"/>
       <x:c r="G7" s="10" t="str"/>
       <x:c r="H7" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/expert-systems-with-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str"/>
       <x:c r="K7" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M7" t="n">
         <x:v>78</x:v>
@@ -623,17 +623,17 @@
       <x:c r="F8" s="10" t="str"/>
       <x:c r="G8" s="10" t="str"/>
       <x:c r="H8" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/fuzzy-sets-and-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str"/>
       <x:c r="K8" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M8" t="n">
         <x:v>78</x:v>
@@ -662,17 +662,17 @@
       <x:c r="F9" s="10" t="str"/>
       <x:c r="G9" s="10" t="str"/>
       <x:c r="H9" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-fusion/articles-in-press</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str"/>
       <x:c r="K9" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M9" t="n">
         <x:v>78</x:v>
@@ -701,17 +701,17 @@
       <x:c r="F10" s="10" t="str"/>
       <x:c r="G10" s="10" t="str"/>
       <x:c r="H10" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-sciences/articles-in-press</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str"/>
       <x:c r="K10" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M10" t="n">
         <x:v>78</x:v>
@@ -740,17 +740,17 @@
       <x:c r="F11" s="10" t="str"/>
       <x:c r="G11" s="10" t="str"/>
       <x:c r="H11" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-approximate-reasoning/articles-in-press</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str"/>
       <x:c r="K11" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M11" t="n">
         <x:v>78</x:v>
@@ -779,17 +779,17 @@
       <x:c r="F12" s="10" t="str"/>
       <x:c r="G12" s="10" t="str"/>
       <x:c r="H12" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-production-economics/articles-in-press</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str"/>
       <x:c r="K12" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L12" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M12" t="n">
         <x:v>78</x:v>
@@ -818,17 +818,17 @@
       <x:c r="F13" s="10" t="str"/>
       <x:c r="G13" s="10" t="str"/>
       <x:c r="H13" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/knowledge-based-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str"/>
       <x:c r="K13" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L13" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M13" t="n">
         <x:v>78</x:v>
@@ -857,17 +857,17 @@
       <x:c r="F14" s="10" t="str"/>
       <x:c r="G14" s="10" t="str"/>
       <x:c r="H14" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/omega/articles-in-press</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str"/>
       <x:c r="K14" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L14" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M14" t="n">
         <x:v>78</x:v>
@@ -896,17 +896,17 @@
       <x:c r="F15" s="10" t="str"/>
       <x:c r="G15" s="10" t="str"/>
       <x:c r="H15" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/engineering-applications-of-artificial-intelligence/articles-in-press</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str"/>
       <x:c r="K15" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L15" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M15" t="n">
         <x:v>78</x:v>
@@ -935,17 +935,17 @@
       <x:c r="F16" s="10" t="str"/>
       <x:c r="G16" s="10" t="str"/>
       <x:c r="H16" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering/articles-in-press</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str"/>
       <x:c r="K16" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L16" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M16" t="n">
         <x:v>78</x:v>
@@ -974,17 +974,17 @@
       <x:c r="F17" s="10" t="str"/>
       <x:c r="G17" s="10" t="str"/>
       <x:c r="H17" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str"/>
       <x:c r="K17" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L17" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M17" t="n">
         <x:v>78</x:v>
@@ -1013,17 +1013,17 @@
       <x:c r="F18" s="10" t="str"/>
       <x:c r="G18" s="10" t="str"/>
       <x:c r="H18" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/international-journal-of-forecasting/articles-in-press</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str"/>
       <x:c r="K18" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L18" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M18" t="n">
         <x:v>78</x:v>
@@ -1052,17 +1052,17 @@
       <x:c r="F19" s="10" t="str"/>
       <x:c r="G19" s="10" t="str"/>
       <x:c r="H19" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-and-management/articles-in-press</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str"/>
       <x:c r="K19" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L19" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M19" t="n">
         <x:v>78</x:v>
@@ -1091,17 +1091,17 @@
       <x:c r="F20" s="10" t="str"/>
       <x:c r="G20" s="10" t="str"/>
       <x:c r="H20" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-systems/articles-in-press</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str"/>
       <x:c r="K20" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L20" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M20" t="n">
         <x:v>78</x:v>
@@ -1130,17 +1130,17 @@
       <x:c r="F21" s="10" t="str"/>
       <x:c r="G21" s="10" t="str"/>
       <x:c r="H21" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/artificial-intelligence/articles-in-press</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str"/>
       <x:c r="K21" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L21" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M21" t="n">
         <x:v>78</x:v>
@@ -1169,17 +1169,17 @@
       <x:c r="F22" s="10" t="str"/>
       <x:c r="G22" s="10" t="str"/>
       <x:c r="H22" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition/articles-in-press</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str"/>
       <x:c r="K22" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L22" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M22" t="n">
         <x:v>78</x:v>
@@ -1208,17 +1208,17 @@
       <x:c r="F23" s="10" t="str"/>
       <x:c r="G23" s="10" t="str"/>
       <x:c r="H23" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/pattern-recognition-letters/articles-in-press</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str"/>
       <x:c r="K23" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L23" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M23" t="n">
         <x:v>78</x:v>
@@ -1247,17 +1247,17 @@
       <x:c r="F24" s="10" t="str"/>
       <x:c r="G24" s="10" t="str"/>
       <x:c r="H24" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/neurocomputing/articles-in-press</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str"/>
       <x:c r="K24" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L24" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M24" t="n">
         <x:v>78</x:v>
@@ -1286,17 +1286,17 @@
       <x:c r="F25" s="10" t="str"/>
       <x:c r="G25" s="10" t="str"/>
       <x:c r="H25" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/physica-a-statistical-mechanics-and-its-applications/articles-in-press</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str"/>
       <x:c r="K25" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L25" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M25" t="n">
         <x:v>78</x:v>
@@ -1325,17 +1325,17 @@
       <x:c r="F26" s="10" t="str"/>
       <x:c r="G26" s="10" t="str"/>
       <x:c r="H26" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety/articles-in-press</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str"/>
       <x:c r="K26" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L26" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M26" t="n">
         <x:v>78</x:v>
@@ -1364,17 +1364,17 @@
       <x:c r="F27" s="10" t="str"/>
       <x:c r="G27" s="10" t="str"/>
       <x:c r="H27" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-biomedical-informatics/articles-in-press</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str"/>
       <x:c r="K27" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L27" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M27" t="n">
         <x:v>78</x:v>
@@ -1401,17 +1401,17 @@
       <x:c r="F28" s="10" t="str"/>
       <x:c r="G28" s="10" t="str"/>
       <x:c r="H28" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/ai-open/articles-in-press</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str"/>
       <x:c r="K28" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L28" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M28" t="n">
         <x:v>78</x:v>
@@ -1440,17 +1440,17 @@
       <x:c r="F29" s="10" t="str"/>
       <x:c r="G29" s="10" t="str"/>
       <x:c r="H29" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/neural-networks/articles-in-press</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str"/>
       <x:c r="K29" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L29" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M29" t="n">
         <x:v>78</x:v>
@@ -1479,17 +1479,17 @@
       <x:c r="F30" s="10" t="str"/>
       <x:c r="G30" s="10" t="str"/>
       <x:c r="H30" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/advanced-engineering-informatics</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str"/>
       <x:c r="K30" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L30" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M30" t="n">
         <x:v>78</x:v>
@@ -1518,17 +1518,17 @@
       <x:c r="F31" s="10" t="str"/>
       <x:c r="G31" s="10" t="str"/>
       <x:c r="H31" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/computers-in-industry/articles-in-press</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str"/>
       <x:c r="K31" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L31" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M31" t="n">
         <x:v>78</x:v>
@@ -1557,17 +1557,17 @@
       <x:c r="F32" s="10" t="str"/>
       <x:c r="G32" s="10" t="str"/>
       <x:c r="H32" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/technological-forecasting-and-social-change/articles-in-press</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str"/>
       <x:c r="K32" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L32" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M32" t="n">
         <x:v>78</x:v>
@@ -1596,17 +1596,17 @@
       <x:c r="F33" s="10" t="str"/>
       <x:c r="G33" s="10" t="str"/>
       <x:c r="H33" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/journal-of-retailing-and-consumer-services/articles-in-press</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str"/>
       <x:c r="K33" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L33" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M33" t="n">
         <x:v>78</x:v>
@@ -1637,17 +1637,17 @@
       </x:c>
       <x:c r="G34" s="10" t="str"/>
       <x:c r="H34" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-b-methodological/articles-in-press</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str"/>
       <x:c r="K34" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L34" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M34" t="n">
         <x:v>78</x:v>
@@ -1678,17 +1678,17 @@
       </x:c>
       <x:c r="G35" s="10" t="str"/>
       <x:c r="H35" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-d-transport-and-environment</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str"/>
       <x:c r="K35" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L35" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M35" t="n">
         <x:v>78</x:v>
@@ -1719,17 +1719,17 @@
       </x:c>
       <x:c r="G36" s="10" t="str"/>
       <x:c r="H36" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/transportation-research-part-e-logistics-and-transportation-review</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str"/>
       <x:c r="K36" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L36" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M36" t="n">
         <x:v>78</x:v>
@@ -1760,17 +1760,17 @@
       </x:c>
       <x:c r="G37" s="10" t="str"/>
       <x:c r="H37" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/information-processing-and-management/articles-in-press</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str"/>
       <x:c r="K37" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L37" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M37" t="n">
         <x:v>78</x:v>
@@ -1799,17 +1799,17 @@
       <x:c r="F38" s="10" t="str"/>
       <x:c r="G38" s="10" t="str"/>
       <x:c r="H38" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/euro-journal-on-decision-processes/articles-in-press</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str"/>
       <x:c r="K38" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L38" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M38" t="n">
         <x:v>78</x:v>
@@ -1838,17 +1838,17 @@
       <x:c r="F39" s="10" t="str"/>
       <x:c r="G39" s="10" t="str"/>
       <x:c r="H39" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/tourism-management/latest</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str"/>
       <x:c r="K39" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L39" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M39" t="n">
         <x:v>78</x:v>
@@ -1877,17 +1877,17 @@
       <x:c r="F40" s="10" t="str"/>
       <x:c r="G40" s="10" t="str"/>
       <x:c r="H40" s="10" t="str">
-        <x:v>elsevier_member_dual_batch</x:v>
+        <x:v>elsevier_member_online_pub_batch</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
         <x:v>https://www.sciencedirect.com/journal/annals-of-tourism-research/articles-in-press</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str"/>
       <x:c r="K40" s="10" t="str">
-        <x:v>direct-rss+crossref-online-update-batch+pending</x:v>
+        <x:v>direct-rss+crossref-online/pub-batch</x:v>
       </x:c>
       <x:c r="L40" s="10" t="str">
-        <x:v>LOCAL V3.2: fast Crossref member-level dual batch (published-online + update-date) is the primary Elsevier discovery path. No hard DOI-prefix filter is applied; the 39-journal ISSN/title whitelist performs final filtering. ScienceDirect API/page remain optional and disabled by default.</x:v>
+        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
       </x:c>
       <x:c r="M40" t="n">
         <x:v>78</x:v>
@@ -3405,13 +3405,13 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
-        <x:v>LOCAL V3.2 build</x:v>
+        <x:v>LOCAL V3.3 build</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>LOCAL-2026.08.19-V3.2</x:v>
+        <x:v>LOCAL-2026.08.19-V3.3</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>Optimized local collector with dual Elsevier Crossref batch and IEEE RSS-date fallback.</x:v>
+        <x:v>Optimized local-only collector.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3419,10 +3419,10 @@
         <x:v>Elsevier strategy</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>Crossref member 78: online-date + update-date → local whitelist</x:v>
+        <x:v>Crossref member 78: online-date + publication-date</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>No hard DOI prefix filter; direct RSS remains optional.</x:v>
+        <x:v>Two-day batch; no update-date scan.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3430,21 +3430,32 @@
         <x:v>IEEE strategy</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>Combined Saved Search RSS → Crossref/IEEE enrichment → RSS pubDate fallback</x:v>
+        <x:v>Combined Saved Search RSS + DOI/title Crossref matching</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>RSS fallback is explicitly labelled and can later be replaced by a stronger publisher/Crossref date.</x:v>
+        <x:v>Whitelist matching by journal/ISSN; RSS pubDate is labelled fallback.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
+        <x:v>Data quality</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>Published status/date never downgraded by pending observations</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>Higher-priority dates are protected.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
         <x:v>Daily window</x:v>
       </x:c>
-      <x:c r="B9" s="10" t="str">
+      <x:c r="B10" s="10" t="str">
         <x:v>2 calendar dates</x:v>
       </x:c>
-      <x:c r="C9" s="10" t="str">
-        <x:v>OVERLAP_DAYS=1 and CROSSREF_DISCOVERY_DAYS=2.</x:v>
+      <x:c r="C10" s="10" t="str">
+        <x:v>Designed for daily Task Scheduler runs.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3534,50 +3545,58 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
-        <x:v>LOCAL V3.2 Elsevier</x:v>
+        <x:v>LOCAL V3.3 Elsevier</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>All 39 Elsevier journals use Crossref member 78 with two batch passes: published-online and update-date. No DOI-prefix hard filter is applied.</x:v>
+        <x:v>Member 78 batch uses published-online first and generic publication-date second. It no longer scans all update-date metadata.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="10" t="str">
-        <x:v>Crossref Member</x:v>
+        <x:v>Generic publication date</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>Publisher/member ID used for batch discovery. Elsevier BV = 78.</x:v>
+        <x:v>Used only as a clearly labelled fallback when Crossref has no explicit published-online value.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="10" t="str">
-        <x:v>Crossref Prefix</x:v>
+        <x:v>IEEE title matching</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>Optional informational/exception field. Blank for the standard V3.2 Elsevier group because final filtering is performed locally by ISSN/title.</x:v>
+        <x:v>If the combined RSS does not expose journal/DOI metadata, the article title is searched in Crossref and accepted only if the result maps to one of the 15 IEEE whitelist journals.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="10" t="str">
-        <x:v>IEEE RSS date</x:v>
+        <x:v>Virtual Journals</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>When IEEE page/Crossref does not yet expose a publication date, the Saved Search RSS pubDate may be used as a clearly labelled fallback date.</x:v>
+        <x:v>Compendia/Virtual Journal labels are rejected unless Crossref maps the underlying article to one of the monitored Transactions/Journals.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="10" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Status protection</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>DOI-bearing records without a usable date remain pending and are rechecked later by DOI only.</x:v>
+        <x:v>A published database row can never be downgraded to pending by a later low-information observation.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="10" t="str">
-        <x:v>Performance</x:v>
+        <x:v>Daily window</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>Elsevier avoids 39–78 per-ISSN calls; IEEE uses one combined feed; Springer remains batch-first.</x:v>
+        <x:v>Yesterday through today (two dates inclusive).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="10" t="str">
+        <x:v>Scheduling</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>Use update_papers_scheduled.bat in Windows Task Scheduler; use update_papers.bat manually.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/paper_monitor_system/journal_list.xlsx
+++ b/paper_monitor_system/journal_list.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="R8333d3755a7c4361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="R9669795b10394d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R6573af0fc7d041ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="Re7468899e7d145bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journals" sheetId="1" r:id="R81622b5044fc4ba5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="R39e8762bdadd4ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R94e5f7e618204b93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Catalog" sheetId="4" r:id="Rdc0e95cb19ec4305"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -313,60 +313,60 @@
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="62" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="72" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="72" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="12" t="str">
         <x:v>Enabled</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="12" t="str">
         <x:v>Publisher</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="12" t="str">
         <x:v>Journal</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="12" t="str">
         <x:v>ISSN</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="12" t="str">
         <x:v>eISSN</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="12" t="str">
         <x:v>Aliases</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="12" t="str">
         <x:v>Category</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="12" t="str">
         <x:v>Mode</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="12" t="str">
         <x:v>Primary URL</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="12" t="str">
         <x:v>RSS URL</x:v>
       </x:c>
-      <x:c r="K1" s="5" t="str">
+      <x:c r="K1" s="12" t="str">
         <x:v>Fallback</x:v>
       </x:c>
-      <x:c r="L1" s="5" t="str">
+      <x:c r="L1" s="12" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="M1" s="20" t="str">
+      <x:c r="M1" s="12" t="str">
         <x:v>Crossref Member</x:v>
       </x:c>
-      <x:c r="N1" s="20" t="str">
+      <x:c r="N1" s="12" t="str">
         <x:v>Crossref Prefix</x:v>
       </x:c>
-      <x:c r="O1" s="20" t="str">
+      <x:c r="O1" s="12" t="str">
         <x:v>Crossref Group</x:v>
       </x:c>
     </x:row>
@@ -389,23 +389,21 @@
       <x:c r="F2" s="10" t="str"/>
       <x:c r="G2" s="10" t="str"/>
       <x:c r="H2" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I2" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/applied-soft-computing/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J2" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I2" s="10"/>
+      <x:c r="J2" s="10"/>
       <x:c r="K2" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L2" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M2" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N2" t="str"/>
-      <x:c r="O2" t="str">
+      <x:c r="N2" s="10"/>
+      <x:c r="O2" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -428,23 +426,21 @@
       <x:c r="F3" s="10" t="str"/>
       <x:c r="G3" s="10" t="str"/>
       <x:c r="H3" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I3" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/computers-and-industrial-engineering/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J3" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I3" s="10"/>
+      <x:c r="J3" s="10"/>
       <x:c r="K3" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L3" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M3" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N3" t="str"/>
-      <x:c r="O3" t="str">
+      <x:c r="N3" s="10"/>
+      <x:c r="O3" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -467,23 +463,21 @@
       <x:c r="F4" s="10" t="str"/>
       <x:c r="G4" s="10" t="str"/>
       <x:c r="H4" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I4" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/computers-and-operations-research/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J4" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I4" s="10"/>
+      <x:c r="J4" s="10"/>
       <x:c r="K4" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L4" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M4" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N4" t="str"/>
-      <x:c r="O4" t="str">
+      <x:c r="N4" s="10"/>
+      <x:c r="O4" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -506,23 +500,21 @@
       <x:c r="F5" s="10" t="str"/>
       <x:c r="G5" s="10" t="str"/>
       <x:c r="H5" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/decision-support-systems/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I5" s="10"/>
+      <x:c r="J5" s="10"/>
       <x:c r="K5" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M5" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N5" t="str"/>
-      <x:c r="O5" t="str">
+      <x:c r="N5" s="10"/>
+      <x:c r="O5" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -545,23 +537,21 @@
       <x:c r="F6" s="10" t="str"/>
       <x:c r="G6" s="10" t="str"/>
       <x:c r="H6" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I6" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/european-journal-of-operational-research/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J6" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I6" s="10"/>
+      <x:c r="J6" s="10"/>
       <x:c r="K6" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M6" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M6" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N6" t="str"/>
-      <x:c r="O6" t="str">
+      <x:c r="N6" s="10"/>
+      <x:c r="O6" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -584,23 +574,21 @@
       <x:c r="F7" s="10" t="str"/>
       <x:c r="G7" s="10" t="str"/>
       <x:c r="H7" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I7" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/expert-systems-with-applications/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J7" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I7" s="10"/>
+      <x:c r="J7" s="10"/>
       <x:c r="K7" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M7" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N7" t="str"/>
-      <x:c r="O7" t="str">
+      <x:c r="N7" s="10"/>
+      <x:c r="O7" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -623,23 +611,21 @@
       <x:c r="F8" s="10" t="str"/>
       <x:c r="G8" s="10" t="str"/>
       <x:c r="H8" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I8" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/fuzzy-sets-and-systems/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J8" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I8" s="10"/>
+      <x:c r="J8" s="10"/>
       <x:c r="K8" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M8" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M8" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N8" t="str"/>
-      <x:c r="O8" t="str">
+      <x:c r="N8" s="10"/>
+      <x:c r="O8" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -662,23 +648,21 @@
       <x:c r="F9" s="10" t="str"/>
       <x:c r="G9" s="10" t="str"/>
       <x:c r="H9" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I9" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/information-fusion/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J9" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I9" s="10"/>
+      <x:c r="J9" s="10"/>
       <x:c r="K9" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M9" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M9" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N9" t="str"/>
-      <x:c r="O9" t="str">
+      <x:c r="N9" s="10"/>
+      <x:c r="O9" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -701,23 +685,21 @@
       <x:c r="F10" s="10" t="str"/>
       <x:c r="G10" s="10" t="str"/>
       <x:c r="H10" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I10" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/information-sciences/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J10" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I10" s="10"/>
+      <x:c r="J10" s="10"/>
       <x:c r="K10" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M10" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M10" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N10" t="str"/>
-      <x:c r="O10" t="str">
+      <x:c r="N10" s="10"/>
+      <x:c r="O10" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -740,23 +722,21 @@
       <x:c r="F11" s="10" t="str"/>
       <x:c r="G11" s="10" t="str"/>
       <x:c r="H11" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I11" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/international-journal-of-approximate-reasoning/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J11" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I11" s="10"/>
+      <x:c r="J11" s="10"/>
       <x:c r="K11" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M11" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M11" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N11" t="str"/>
-      <x:c r="O11" t="str">
+      <x:c r="N11" s="10"/>
+      <x:c r="O11" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -779,23 +759,21 @@
       <x:c r="F12" s="10" t="str"/>
       <x:c r="G12" s="10" t="str"/>
       <x:c r="H12" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I12" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/international-journal-of-production-economics/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J12" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I12" s="10"/>
+      <x:c r="J12" s="10"/>
       <x:c r="K12" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L12" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M12" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M12" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N12" t="str"/>
-      <x:c r="O12" t="str">
+      <x:c r="N12" s="10"/>
+      <x:c r="O12" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -818,23 +796,21 @@
       <x:c r="F13" s="10" t="str"/>
       <x:c r="G13" s="10" t="str"/>
       <x:c r="H13" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I13" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/knowledge-based-systems/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J13" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I13" s="10"/>
+      <x:c r="J13" s="10"/>
       <x:c r="K13" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L13" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M13" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M13" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N13" t="str"/>
-      <x:c r="O13" t="str">
+      <x:c r="N13" s="10"/>
+      <x:c r="O13" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -857,23 +833,21 @@
       <x:c r="F14" s="10" t="str"/>
       <x:c r="G14" s="10" t="str"/>
       <x:c r="H14" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I14" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/omega/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J14" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I14" s="10"/>
+      <x:c r="J14" s="10"/>
       <x:c r="K14" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L14" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M14" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M14" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N14" t="str"/>
-      <x:c r="O14" t="str">
+      <x:c r="N14" s="10"/>
+      <x:c r="O14" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -896,23 +870,21 @@
       <x:c r="F15" s="10" t="str"/>
       <x:c r="G15" s="10" t="str"/>
       <x:c r="H15" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I15" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/engineering-applications-of-artificial-intelligence/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J15" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I15" s="10"/>
+      <x:c r="J15" s="10"/>
       <x:c r="K15" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L15" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M15" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M15" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N15" t="str"/>
-      <x:c r="O15" t="str">
+      <x:c r="N15" s="10"/>
+      <x:c r="O15" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -935,23 +907,21 @@
       <x:c r="F16" s="10" t="str"/>
       <x:c r="G16" s="10" t="str"/>
       <x:c r="H16" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I16" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J16" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I16" s="10"/>
+      <x:c r="J16" s="10"/>
       <x:c r="K16" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L16" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M16" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M16" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N16" t="str"/>
-      <x:c r="O16" t="str">
+      <x:c r="N16" s="10"/>
+      <x:c r="O16" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -974,23 +944,21 @@
       <x:c r="F17" s="10" t="str"/>
       <x:c r="G17" s="10" t="str"/>
       <x:c r="H17" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I17" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J17" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I17" s="10"/>
+      <x:c r="J17" s="10"/>
       <x:c r="K17" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L17" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M17" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M17" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N17" t="str"/>
-      <x:c r="O17" t="str">
+      <x:c r="N17" s="10"/>
+      <x:c r="O17" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1013,23 +981,21 @@
       <x:c r="F18" s="10" t="str"/>
       <x:c r="G18" s="10" t="str"/>
       <x:c r="H18" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I18" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/international-journal-of-forecasting/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J18" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I18" s="10"/>
+      <x:c r="J18" s="10"/>
       <x:c r="K18" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L18" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M18" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M18" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N18" t="str"/>
-      <x:c r="O18" t="str">
+      <x:c r="N18" s="10"/>
+      <x:c r="O18" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1052,23 +1018,21 @@
       <x:c r="F19" s="10" t="str"/>
       <x:c r="G19" s="10" t="str"/>
       <x:c r="H19" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I19" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/information-and-management/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J19" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I19" s="10"/>
+      <x:c r="J19" s="10"/>
       <x:c r="K19" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L19" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M19" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M19" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N19" t="str"/>
-      <x:c r="O19" t="str">
+      <x:c r="N19" s="10"/>
+      <x:c r="O19" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1091,23 +1055,21 @@
       <x:c r="F20" s="10" t="str"/>
       <x:c r="G20" s="10" t="str"/>
       <x:c r="H20" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I20" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/information-systems/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J20" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I20" s="10"/>
+      <x:c r="J20" s="10"/>
       <x:c r="K20" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L20" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M20" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M20" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N20" t="str"/>
-      <x:c r="O20" t="str">
+      <x:c r="N20" s="10"/>
+      <x:c r="O20" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1130,23 +1092,21 @@
       <x:c r="F21" s="10" t="str"/>
       <x:c r="G21" s="10" t="str"/>
       <x:c r="H21" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I21" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/artificial-intelligence/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J21" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I21" s="10"/>
+      <x:c r="J21" s="10"/>
       <x:c r="K21" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L21" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M21" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M21" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N21" t="str"/>
-      <x:c r="O21" t="str">
+      <x:c r="N21" s="10"/>
+      <x:c r="O21" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1169,23 +1129,21 @@
       <x:c r="F22" s="10" t="str"/>
       <x:c r="G22" s="10" t="str"/>
       <x:c r="H22" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I22" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/pattern-recognition/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J22" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I22" s="10"/>
+      <x:c r="J22" s="10"/>
       <x:c r="K22" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L22" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M22" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M22" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N22" t="str"/>
-      <x:c r="O22" t="str">
+      <x:c r="N22" s="10"/>
+      <x:c r="O22" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1208,23 +1166,21 @@
       <x:c r="F23" s="10" t="str"/>
       <x:c r="G23" s="10" t="str"/>
       <x:c r="H23" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I23" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/pattern-recognition-letters/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J23" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I23" s="10"/>
+      <x:c r="J23" s="10"/>
       <x:c r="K23" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L23" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M23" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M23" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N23" t="str"/>
-      <x:c r="O23" t="str">
+      <x:c r="N23" s="10"/>
+      <x:c r="O23" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1247,23 +1203,21 @@
       <x:c r="F24" s="10" t="str"/>
       <x:c r="G24" s="10" t="str"/>
       <x:c r="H24" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I24" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/neurocomputing/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J24" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I24" s="10"/>
+      <x:c r="J24" s="10"/>
       <x:c r="K24" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L24" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M24" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M24" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N24" t="str"/>
-      <x:c r="O24" t="str">
+      <x:c r="N24" s="10"/>
+      <x:c r="O24" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1286,23 +1240,21 @@
       <x:c r="F25" s="10" t="str"/>
       <x:c r="G25" s="10" t="str"/>
       <x:c r="H25" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I25" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/physica-a-statistical-mechanics-and-its-applications/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J25" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I25" s="10"/>
+      <x:c r="J25" s="10"/>
       <x:c r="K25" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L25" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M25" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M25" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N25" t="str"/>
-      <x:c r="O25" t="str">
+      <x:c r="N25" s="10"/>
+      <x:c r="O25" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1325,23 +1277,21 @@
       <x:c r="F26" s="10" t="str"/>
       <x:c r="G26" s="10" t="str"/>
       <x:c r="H26" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I26" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J26" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I26" s="10"/>
+      <x:c r="J26" s="10"/>
       <x:c r="K26" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L26" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M26" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M26" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N26" t="str"/>
-      <x:c r="O26" t="str">
+      <x:c r="N26" s="10"/>
+      <x:c r="O26" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1364,23 +1314,21 @@
       <x:c r="F27" s="10" t="str"/>
       <x:c r="G27" s="10" t="str"/>
       <x:c r="H27" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I27" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/journal-of-biomedical-informatics/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J27" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I27" s="10"/>
+      <x:c r="J27" s="10"/>
       <x:c r="K27" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L27" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M27" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M27" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N27" t="str"/>
-      <x:c r="O27" t="str">
+      <x:c r="N27" s="10"/>
+      <x:c r="O27" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1401,23 +1349,21 @@
       <x:c r="F28" s="10" t="str"/>
       <x:c r="G28" s="10" t="str"/>
       <x:c r="H28" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I28" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/ai-open/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J28" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I28" s="10"/>
+      <x:c r="J28" s="10"/>
       <x:c r="K28" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L28" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M28" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M28" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N28" t="str"/>
-      <x:c r="O28" t="str">
+      <x:c r="N28" s="10"/>
+      <x:c r="O28" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1440,23 +1386,21 @@
       <x:c r="F29" s="10" t="str"/>
       <x:c r="G29" s="10" t="str"/>
       <x:c r="H29" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I29" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/neural-networks/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J29" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I29" s="10"/>
+      <x:c r="J29" s="10"/>
       <x:c r="K29" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L29" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M29" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N29" t="str"/>
-      <x:c r="O29" t="str">
+      <x:c r="N29" s="10"/>
+      <x:c r="O29" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1479,23 +1423,21 @@
       <x:c r="F30" s="10" t="str"/>
       <x:c r="G30" s="10" t="str"/>
       <x:c r="H30" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I30" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/advanced-engineering-informatics</x:v>
-      </x:c>
-      <x:c r="J30" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I30" s="10"/>
+      <x:c r="J30" s="10"/>
       <x:c r="K30" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L30" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M30" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M30" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N30" t="str"/>
-      <x:c r="O30" t="str">
+      <x:c r="N30" s="10"/>
+      <x:c r="O30" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1518,23 +1460,21 @@
       <x:c r="F31" s="10" t="str"/>
       <x:c r="G31" s="10" t="str"/>
       <x:c r="H31" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I31" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/computers-in-industry/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J31" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I31" s="10"/>
+      <x:c r="J31" s="10"/>
       <x:c r="K31" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L31" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M31" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M31" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N31" t="str"/>
-      <x:c r="O31" t="str">
+      <x:c r="N31" s="10"/>
+      <x:c r="O31" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1557,23 +1497,21 @@
       <x:c r="F32" s="10" t="str"/>
       <x:c r="G32" s="10" t="str"/>
       <x:c r="H32" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I32" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/technological-forecasting-and-social-change/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J32" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I32" s="10"/>
+      <x:c r="J32" s="10"/>
       <x:c r="K32" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L32" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M32" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M32" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N32" t="str"/>
-      <x:c r="O32" t="str">
+      <x:c r="N32" s="10"/>
+      <x:c r="O32" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1596,23 +1534,21 @@
       <x:c r="F33" s="10" t="str"/>
       <x:c r="G33" s="10" t="str"/>
       <x:c r="H33" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I33" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/journal-of-retailing-and-consumer-services/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J33" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I33" s="10"/>
+      <x:c r="J33" s="10"/>
       <x:c r="K33" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L33" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M33" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M33" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N33" t="str"/>
-      <x:c r="O33" t="str">
+      <x:c r="N33" s="10"/>
+      <x:c r="O33" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1637,23 +1573,21 @@
       </x:c>
       <x:c r="G34" s="10" t="str"/>
       <x:c r="H34" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I34" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/transportation-research-part-b-methodological/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J34" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I34" s="10"/>
+      <x:c r="J34" s="10"/>
       <x:c r="K34" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L34" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M34" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M34" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N34" t="str"/>
-      <x:c r="O34" t="str">
+      <x:c r="N34" s="10"/>
+      <x:c r="O34" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1678,23 +1612,21 @@
       </x:c>
       <x:c r="G35" s="10" t="str"/>
       <x:c r="H35" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I35" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/transportation-research-part-d-transport-and-environment</x:v>
-      </x:c>
-      <x:c r="J35" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I35" s="10"/>
+      <x:c r="J35" s="10"/>
       <x:c r="K35" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L35" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M35" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M35" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N35" t="str"/>
-      <x:c r="O35" t="str">
+      <x:c r="N35" s="10"/>
+      <x:c r="O35" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1719,23 +1651,21 @@
       </x:c>
       <x:c r="G36" s="10" t="str"/>
       <x:c r="H36" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I36" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/transportation-research-part-e-logistics-and-transportation-review</x:v>
-      </x:c>
-      <x:c r="J36" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I36" s="10"/>
+      <x:c r="J36" s="10"/>
       <x:c r="K36" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L36" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M36" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M36" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N36" t="str"/>
-      <x:c r="O36" t="str">
+      <x:c r="N36" s="10"/>
+      <x:c r="O36" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1760,23 +1690,21 @@
       </x:c>
       <x:c r="G37" s="10" t="str"/>
       <x:c r="H37" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I37" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/information-processing-and-management/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J37" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I37" s="10"/>
+      <x:c r="J37" s="10"/>
       <x:c r="K37" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L37" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M37" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M37" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N37" t="str"/>
-      <x:c r="O37" t="str">
+      <x:c r="N37" s="10"/>
+      <x:c r="O37" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1799,23 +1727,21 @@
       <x:c r="F38" s="10" t="str"/>
       <x:c r="G38" s="10" t="str"/>
       <x:c r="H38" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I38" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/euro-journal-on-decision-processes/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J38" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I38" s="10"/>
+      <x:c r="J38" s="10"/>
       <x:c r="K38" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L38" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M38" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M38" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N38" t="str"/>
-      <x:c r="O38" t="str">
+      <x:c r="N38" s="10"/>
+      <x:c r="O38" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1838,23 +1764,21 @@
       <x:c r="F39" s="10" t="str"/>
       <x:c r="G39" s="10" t="str"/>
       <x:c r="H39" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I39" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/tourism-management/latest</x:v>
-      </x:c>
-      <x:c r="J39" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I39" s="10"/>
+      <x:c r="J39" s="10"/>
       <x:c r="K39" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L39" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M39" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M39" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N39" t="str"/>
-      <x:c r="O39" t="str">
+      <x:c r="N39" s="10"/>
+      <x:c r="O39" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1877,23 +1801,21 @@
       <x:c r="F40" s="10" t="str"/>
       <x:c r="G40" s="10" t="str"/>
       <x:c r="H40" s="10" t="str">
-        <x:v>elsevier_member_online_pub_batch</x:v>
-      </x:c>
-      <x:c r="I40" s="10" t="str">
-        <x:v>https://www.sciencedirect.com/journal/annals-of-tourism-research/articles-in-press</x:v>
-      </x:c>
-      <x:c r="J40" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I40" s="10"/>
+      <x:c r="J40" s="10"/>
       <x:c r="K40" s="10" t="str">
-        <x:v>direct-rss+crossref-online/pub-batch</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L40" s="10" t="str">
-        <x:v>LOCAL V3.3: Crossref member 78 two-day batch. Pass 1 uses explicit published-online; Pass 2 uses generic publication date as a clearly labelled fallback. ScienceDirect API/page remain optional; stable direct RSS can still supplement.</x:v>
-      </x:c>
-      <x:c r="M40" t="n">
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M40" s="10" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="N40" t="str"/>
-      <x:c r="O40" t="str">
+      <x:c r="N40" s="10"/>
+      <x:c r="O40" s="10" t="str">
         <x:v>Elsevier-78</x:v>
       </x:c>
     </x:row>
@@ -1916,21 +1838,23 @@
       <x:c r="F41" s="10" t="str"/>
       <x:c r="G41" s="10" t="str"/>
       <x:c r="H41" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I41" s="10" t="str">
-        <x:v>http://link.springer.com/journal/10479/articles</x:v>
-      </x:c>
-      <x:c r="J41" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I41" s="10"/>
+      <x:c r="J41" s="10"/>
       <x:c r="K41" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L41" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M41"/>
-      <x:c r="N41"/>
-      <x:c r="O41"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M41" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N41" s="10"/>
+      <x:c r="O41" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="n">
@@ -1951,21 +1875,23 @@
       <x:c r="F42" s="10" t="str"/>
       <x:c r="G42" s="10" t="str"/>
       <x:c r="H42" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I42" s="10" t="str">
-        <x:v>http://link.springer.com/journal/10700/articles</x:v>
-      </x:c>
-      <x:c r="J42" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I42" s="10"/>
+      <x:c r="J42" s="10"/>
       <x:c r="K42" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L42" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M42"/>
-      <x:c r="N42"/>
-      <x:c r="O42"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M42" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N42" s="10"/>
+      <x:c r="O42" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="n">
@@ -1986,21 +1912,23 @@
       <x:c r="F43" s="10" t="str"/>
       <x:c r="G43" s="10" t="str"/>
       <x:c r="H43" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I43" s="10" t="str">
-        <x:v>http://link.springer.com/journal/10726/articles</x:v>
-      </x:c>
-      <x:c r="J43" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I43" s="10"/>
+      <x:c r="J43" s="10"/>
       <x:c r="K43" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L43" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M43"/>
-      <x:c r="N43"/>
-      <x:c r="O43"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M43" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N43" s="10"/>
+      <x:c r="O43" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="n">
@@ -2021,21 +1949,23 @@
       <x:c r="F44" s="10" t="str"/>
       <x:c r="G44" s="10" t="str"/>
       <x:c r="H44" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I44" s="10" t="str">
-        <x:v>http://link.springer.com/journal/500/articles</x:v>
-      </x:c>
-      <x:c r="J44" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I44" s="10"/>
+      <x:c r="J44" s="10"/>
       <x:c r="K44" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L44" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M44"/>
-      <x:c r="N44"/>
-      <x:c r="O44"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M44" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N44" s="10"/>
+      <x:c r="O44" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="n">
@@ -2056,21 +1986,23 @@
       <x:c r="F45" s="10" t="str"/>
       <x:c r="G45" s="10" t="str"/>
       <x:c r="H45" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I45" s="10" t="str">
-        <x:v>http://link.springer.com/journal/13042/articles</x:v>
-      </x:c>
-      <x:c r="J45" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I45" s="10"/>
+      <x:c r="J45" s="10"/>
       <x:c r="K45" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L45" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M45"/>
-      <x:c r="N45"/>
-      <x:c r="O45"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M45" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N45" s="10"/>
+      <x:c r="O45" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="n">
@@ -2091,21 +2023,23 @@
       <x:c r="F46" s="10" t="str"/>
       <x:c r="G46" s="10" t="str"/>
       <x:c r="H46" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I46" s="10" t="str">
-        <x:v>http://link.springer.com/journal/10115/articles</x:v>
-      </x:c>
-      <x:c r="J46" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I46" s="10"/>
+      <x:c r="J46" s="10"/>
       <x:c r="K46" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L46" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M46"/>
-      <x:c r="N46"/>
-      <x:c r="O46"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M46" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N46" s="10"/>
+      <x:c r="O46" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="n">
@@ -2126,21 +2060,23 @@
       <x:c r="F47" s="10" t="str"/>
       <x:c r="G47" s="10" t="str"/>
       <x:c r="H47" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I47" s="10" t="str">
-        <x:v>http://link.springer.com/journal/521/articles</x:v>
-      </x:c>
-      <x:c r="J47" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I47" s="10"/>
+      <x:c r="J47" s="10"/>
       <x:c r="K47" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L47" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M47"/>
-      <x:c r="N47"/>
-      <x:c r="O47"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M47" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N47" s="10"/>
+      <x:c r="O47" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="n">
@@ -2161,21 +2097,23 @@
       <x:c r="F48" s="10" t="str"/>
       <x:c r="G48" s="10" t="str"/>
       <x:c r="H48" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I48" s="10" t="str">
-        <x:v>http://link.springer.com/journal/10489/articles</x:v>
-      </x:c>
-      <x:c r="J48" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I48" s="10"/>
+      <x:c r="J48" s="10"/>
       <x:c r="K48" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L48" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M48"/>
-      <x:c r="N48"/>
-      <x:c r="O48"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M48" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N48" s="10"/>
+      <x:c r="O48" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="n">
@@ -2196,21 +2134,23 @@
       <x:c r="F49" s="10" t="str"/>
       <x:c r="G49" s="10" t="str"/>
       <x:c r="H49" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I49" s="10" t="str">
-        <x:v>http://link.springer.com/journal/12559/articles</x:v>
-      </x:c>
-      <x:c r="J49" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I49" s="10"/>
+      <x:c r="J49" s="10"/>
       <x:c r="K49" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L49" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M49"/>
-      <x:c r="N49"/>
-      <x:c r="O49"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M49" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N49" s="10"/>
+      <x:c r="O49" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="n">
@@ -2233,21 +2173,23 @@
       </x:c>
       <x:c r="G50" s="10" t="str"/>
       <x:c r="H50" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I50" s="10" t="str">
-        <x:v>http://link.springer.com/journal/40747/articles</x:v>
-      </x:c>
-      <x:c r="J50" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I50" s="10"/>
+      <x:c r="J50" s="10"/>
       <x:c r="K50" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L50" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M50"/>
-      <x:c r="N50"/>
-      <x:c r="O50"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M50" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N50" s="10"/>
+      <x:c r="O50" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="n">
@@ -2268,21 +2210,23 @@
       <x:c r="F51" s="10" t="str"/>
       <x:c r="G51" s="10" t="str"/>
       <x:c r="H51" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I51" s="10" t="str">
-        <x:v>http://link.springer.com/journal/40815/articles</x:v>
-      </x:c>
-      <x:c r="J51" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I51" s="10"/>
+      <x:c r="J51" s="10"/>
       <x:c r="K51" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L51" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M51"/>
-      <x:c r="N51"/>
-      <x:c r="O51"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M51" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N51" s="10"/>
+      <x:c r="O51" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="n">
@@ -2303,21 +2247,23 @@
       <x:c r="F52" s="10" t="str"/>
       <x:c r="G52" s="10" t="str"/>
       <x:c r="H52" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I52" s="10" t="str">
-        <x:v>http://link.springer.com/journal/291/articles</x:v>
-      </x:c>
-      <x:c r="J52" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I52" s="10"/>
+      <x:c r="J52" s="10"/>
       <x:c r="K52" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L52" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M52"/>
-      <x:c r="N52"/>
-      <x:c r="O52"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M52" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N52" s="10"/>
+      <x:c r="O52" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="n">
@@ -2338,21 +2284,23 @@
       <x:c r="F53" s="10" t="str"/>
       <x:c r="G53" s="10" t="str"/>
       <x:c r="H53" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I53" s="10" t="str">
-        <x:v>https://link.springer.com/journal/10462/articles</x:v>
-      </x:c>
-      <x:c r="J53" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I53" s="10"/>
+      <x:c r="J53" s="10"/>
       <x:c r="K53" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L53" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M53"/>
-      <x:c r="N53"/>
-      <x:c r="O53"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M53" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N53" s="10"/>
+      <x:c r="O53" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="n">
@@ -2375,21 +2323,23 @@
       </x:c>
       <x:c r="G54" s="10" t="str"/>
       <x:c r="H54" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I54" s="10" t="str">
-        <x:v>https://link.springer.com/journal/42524/articles</x:v>
-      </x:c>
-      <x:c r="J54" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I54" s="10"/>
+      <x:c r="J54" s="10"/>
       <x:c r="K54" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L54" s="10" t="str">
-        <x:v>Renamed from Frontiers of Engineering Management in January 2026. Former pISSN/eISSN: 2095-7513 / 2096-0255. Current ISSNs are used for live monitoring. LOCAL V2: batch Meta API first; per-journal API/Online First/Crossref fallback.</x:v>
-      </x:c>
-      <x:c r="M54"/>
-      <x:c r="N54"/>
-      <x:c r="O54"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M54" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N54" s="10"/>
+      <x:c r="O54" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="n">
@@ -2410,21 +2360,23 @@
       <x:c r="F55" s="10" t="str"/>
       <x:c r="G55" s="10" t="str"/>
       <x:c r="H55" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I55" s="10" t="str">
-        <x:v>http://link.springer.com/journal/11518/articles</x:v>
-      </x:c>
-      <x:c r="J55" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I55" s="10"/>
+      <x:c r="J55" s="10"/>
       <x:c r="K55" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L55" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M55"/>
-      <x:c r="N55"/>
-      <x:c r="O55"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M55" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N55" s="10"/>
+      <x:c r="O55" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="10" t="n">
@@ -2445,21 +2397,23 @@
       <x:c r="F56" s="10" t="str"/>
       <x:c r="G56" s="10" t="str"/>
       <x:c r="H56" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I56" s="10" t="str">
-        <x:v>http://link.springer.com/journal/11424/articles</x:v>
-      </x:c>
-      <x:c r="J56" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I56" s="10"/>
+      <x:c r="J56" s="10"/>
       <x:c r="K56" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L56" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M56"/>
-      <x:c r="N56"/>
-      <x:c r="O56"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M56" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N56" s="10"/>
+      <x:c r="O56" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="10" t="n">
@@ -2482,21 +2436,23 @@
       </x:c>
       <x:c r="G57" s="10" t="str"/>
       <x:c r="H57" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I57" s="10" t="str">
-        <x:v>http://link.springer.com/journal/10618/articles</x:v>
-      </x:c>
-      <x:c r="J57" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I57" s="10"/>
+      <x:c r="J57" s="10"/>
       <x:c r="K57" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L57" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M57"/>
-      <x:c r="N57"/>
-      <x:c r="O57"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M57" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N57" s="10"/>
+      <x:c r="O57" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="10" t="n">
@@ -2517,21 +2473,23 @@
       <x:c r="F58" s="10" t="str"/>
       <x:c r="G58" s="10" t="str"/>
       <x:c r="H58" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I58" s="10" t="str">
-        <x:v>https://link.springer.com/journal/13278/articles</x:v>
-      </x:c>
-      <x:c r="J58" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I58" s="10"/>
+      <x:c r="J58" s="10"/>
       <x:c r="K58" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L58" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M58"/>
-      <x:c r="N58"/>
-      <x:c r="O58"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M58" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N58" s="10"/>
+      <x:c r="O58" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="10" t="n">
@@ -2552,21 +2510,23 @@
       <x:c r="F59" s="10" t="str"/>
       <x:c r="G59" s="10" t="str"/>
       <x:c r="H59" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I59" s="10" t="str">
-        <x:v>http://link.springer.com/journal/10729/articles</x:v>
-      </x:c>
-      <x:c r="J59" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I59" s="10"/>
+      <x:c r="J59" s="10"/>
       <x:c r="K59" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L59" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M59"/>
-      <x:c r="N59"/>
-      <x:c r="O59"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M59" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N59" s="10"/>
+      <x:c r="O59" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="n">
@@ -2587,21 +2547,23 @@
       <x:c r="F60" s="10" t="str"/>
       <x:c r="G60" s="10" t="str"/>
       <x:c r="H60" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I60" s="10" t="str">
-        <x:v>http://link.springer.com/journal/10660/articles</x:v>
-      </x:c>
-      <x:c r="J60" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I60" s="10"/>
+      <x:c r="J60" s="10"/>
       <x:c r="K60" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L60" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M60"/>
-      <x:c r="N60"/>
-      <x:c r="O60"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M60" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N60" s="10"/>
+      <x:c r="O60" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="n">
@@ -2622,21 +2584,23 @@
       <x:c r="F61" s="10" t="str"/>
       <x:c r="G61" s="10" t="str"/>
       <x:c r="H61" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I61" s="10" t="str">
-        <x:v>http://link.springer.com/journal/12351/articles</x:v>
-      </x:c>
-      <x:c r="J61" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I61" s="10"/>
+      <x:c r="J61" s="10"/>
       <x:c r="K61" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L61" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M61"/>
-      <x:c r="N61"/>
-      <x:c r="O61"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M61" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N61" s="10"/>
+      <x:c r="O61" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="n">
@@ -2657,21 +2621,23 @@
       <x:c r="F62" s="10" t="str"/>
       <x:c r="G62" s="10" t="str"/>
       <x:c r="H62" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I62" s="10" t="str">
-        <x:v>http://link.springer.com/journal/11750/articles</x:v>
-      </x:c>
-      <x:c r="J62" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I62" s="10"/>
+      <x:c r="J62" s="10"/>
       <x:c r="K62" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L62" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M62"/>
-      <x:c r="N62"/>
-      <x:c r="O62"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M62" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N62" s="10"/>
+      <x:c r="O62" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="n">
@@ -2692,21 +2658,23 @@
       <x:c r="F63" s="10" t="str"/>
       <x:c r="G63" s="10" t="str"/>
       <x:c r="H63" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I63" s="10" t="str">
-        <x:v>http://link.springer.com/journal/11238/articles</x:v>
-      </x:c>
-      <x:c r="J63" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I63" s="10"/>
+      <x:c r="J63" s="10"/>
       <x:c r="K63" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L63" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M63"/>
-      <x:c r="N63"/>
-      <x:c r="O63"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M63" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N63" s="10"/>
+      <x:c r="O63" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="n">
@@ -2727,21 +2695,23 @@
       <x:c r="F64" s="10" t="str"/>
       <x:c r="G64" s="10" t="str"/>
       <x:c r="H64" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I64" s="10" t="str">
-        <x:v>http://link.springer.com/journal/10100/articles</x:v>
-      </x:c>
-      <x:c r="J64" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I64" s="10"/>
+      <x:c r="J64" s="10"/>
       <x:c r="K64" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L64" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M64"/>
-      <x:c r="N64"/>
-      <x:c r="O64"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M64" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N64" s="10"/>
+      <x:c r="O64" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="n">
@@ -2762,21 +2732,23 @@
       <x:c r="F65" s="10" t="str"/>
       <x:c r="G65" s="10" t="str"/>
       <x:c r="H65" s="10" t="str">
-        <x:v>springer_batch_api</x:v>
-      </x:c>
-      <x:c r="I65" s="10" t="str">
-        <x:v>https://www.springer.com/journal/44196</x:v>
-      </x:c>
-      <x:c r="J65" s="10" t="str"/>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I65" s="10"/>
+      <x:c r="J65" s="10"/>
       <x:c r="K65" s="10" t="str">
-        <x:v>per-journal-api+online-first+crossref</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L65" s="10" t="str">
-        <x:v>LOCAL V2: Try one date-window Springer Meta API query and filter locally to the 25-journal whitelist. If batch querying fails, fall back to per-journal Meta API, Online First page, then Crossref.</x:v>
-      </x:c>
-      <x:c r="M65"/>
-      <x:c r="N65"/>
-      <x:c r="O65"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M65" s="10" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="N65" s="10"/>
+      <x:c r="O65" s="10" t="str">
+        <x:v>Springer-297</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="n">
@@ -2797,23 +2769,23 @@
       <x:c r="F66" s="10" t="str"/>
       <x:c r="G66" s="10" t="str"/>
       <x:c r="H66" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I66" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=6376248&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J66" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I66" s="10"/>
+      <x:c r="J66" s="10"/>
       <x:c r="K66" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L66" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M66"/>
-      <x:c r="N66"/>
-      <x:c r="O66"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M66" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N66" s="10"/>
+      <x:c r="O66" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="n">
@@ -2834,23 +2806,23 @@
       <x:c r="F67" s="10" t="str"/>
       <x:c r="G67" s="10" t="str"/>
       <x:c r="H67" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I67" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=6352949&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J67" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I67" s="10"/>
+      <x:c r="J67" s="10"/>
       <x:c r="K67" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L67" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M67"/>
-      <x:c r="N67"/>
-      <x:c r="O67"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M67" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N67" s="10"/>
+      <x:c r="O67" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="n">
@@ -2869,23 +2841,23 @@
       <x:c r="F68" s="10" t="str"/>
       <x:c r="G68" s="10" t="str"/>
       <x:c r="H68" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I68" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=6780646&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J68" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I68" s="10"/>
+      <x:c r="J68" s="10"/>
       <x:c r="K68" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L68" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M68"/>
-      <x:c r="N68"/>
-      <x:c r="O68"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M68" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N68" s="10"/>
+      <x:c r="O68" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="n">
@@ -2906,23 +2878,23 @@
       <x:c r="F69" s="10" t="str"/>
       <x:c r="G69" s="10" t="str"/>
       <x:c r="H69" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I69" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=4358784&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J69" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I69" s="10"/>
+      <x:c r="J69" s="10"/>
       <x:c r="K69" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L69" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M69"/>
-      <x:c r="N69"/>
-      <x:c r="O69"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M69" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N69" s="10"/>
+      <x:c r="O69" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="n">
@@ -2943,23 +2915,23 @@
       <x:c r="F70" s="10" t="str"/>
       <x:c r="G70" s="10" t="str"/>
       <x:c r="H70" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I70" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=4378406&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J70" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I70" s="10"/>
+      <x:c r="J70" s="10"/>
       <x:c r="K70" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L70" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M70"/>
-      <x:c r="N70"/>
-      <x:c r="O70"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M70" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N70" s="10"/>
+      <x:c r="O70" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="n">
@@ -2980,23 +2952,23 @@
       <x:c r="F71" s="10" t="str"/>
       <x:c r="G71" s="10" t="str"/>
       <x:c r="H71" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I71" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=4429834&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J71" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I71" s="10"/>
+      <x:c r="J71" s="10"/>
       <x:c r="K71" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L71" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M71"/>
-      <x:c r="N71"/>
-      <x:c r="O71"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M71" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N71" s="10"/>
+      <x:c r="O71" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10" t="n">
@@ -3015,23 +2987,23 @@
       <x:c r="F72" s="10" t="str"/>
       <x:c r="G72" s="10" t="str"/>
       <x:c r="H72" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I72" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=9184921</x:v>
-      </x:c>
-      <x:c r="J72" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I72" s="10"/>
+      <x:c r="J72" s="10"/>
       <x:c r="K72" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L72" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M72"/>
-      <x:c r="N72"/>
-      <x:c r="O72"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M72" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N72" s="10"/>
+      <x:c r="O72" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10" t="n">
@@ -3052,23 +3024,23 @@
       <x:c r="F73" s="10" t="str"/>
       <x:c r="G73" s="10" t="str"/>
       <x:c r="H73" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I73" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=4358933&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J73" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I73" s="10"/>
+      <x:c r="J73" s="10"/>
       <x:c r="K73" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L73" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M73"/>
-      <x:c r="N73"/>
-      <x:c r="O73"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M73" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N73" s="10"/>
+      <x:c r="O73" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="n">
@@ -3089,23 +3061,23 @@
       <x:c r="F74" s="10" t="str"/>
       <x:c r="G74" s="10" t="str"/>
       <x:c r="H74" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I74" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=4358751&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J74" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I74" s="10"/>
+      <x:c r="J74" s="10"/>
       <x:c r="K74" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L74" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M74"/>
-      <x:c r="N74"/>
-      <x:c r="O74"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M74" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N74" s="10"/>
+      <x:c r="O74" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="n">
@@ -3126,23 +3098,23 @@
       <x:c r="F75" s="10" t="str"/>
       <x:c r="G75" s="10" t="str"/>
       <x:c r="H75" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I75" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=6104215&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J75" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I75" s="10"/>
+      <x:c r="J75" s="10"/>
       <x:c r="K75" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L75" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M75"/>
-      <x:c r="N75"/>
-      <x:c r="O75"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M75" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N75" s="10"/>
+      <x:c r="O75" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="n">
@@ -3163,23 +3135,23 @@
       <x:c r="F76" s="10" t="str"/>
       <x:c r="G76" s="10" t="str"/>
       <x:c r="H76" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I76" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=4359286</x:v>
-      </x:c>
-      <x:c r="J76" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I76" s="10"/>
+      <x:c r="J76" s="10"/>
       <x:c r="K76" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L76" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M76"/>
-      <x:c r="N76"/>
-      <x:c r="O76"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M76" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N76" s="10"/>
+      <x:c r="O76" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="n">
@@ -3198,23 +3170,23 @@
       <x:c r="F77" s="10" t="str"/>
       <x:c r="G77" s="10" t="str"/>
       <x:c r="H77" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I77" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=7153538&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J77" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I77" s="10"/>
+      <x:c r="J77" s="10"/>
       <x:c r="K77" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L77" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M77"/>
-      <x:c r="N77"/>
-      <x:c r="O77"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M77" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N77" s="10"/>
+      <x:c r="O77" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="n">
@@ -3233,23 +3205,23 @@
       <x:c r="F78" s="10" t="str"/>
       <x:c r="G78" s="10" t="str"/>
       <x:c r="H78" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I78" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=6930788&amp;sortType=newest</x:v>
-      </x:c>
-      <x:c r="J78" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I78" s="10"/>
+      <x:c r="J78" s="10"/>
       <x:c r="K78" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L78" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M78"/>
-      <x:c r="N78"/>
-      <x:c r="O78"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M78" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N78" s="10"/>
+      <x:c r="O78" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="n">
@@ -3270,23 +3242,23 @@
       <x:c r="F79" s="10" t="str"/>
       <x:c r="G79" s="10" t="str"/>
       <x:c r="H79" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I79" s="10" t="str">
-        <x:v>IEEE|https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=7725587</x:v>
-      </x:c>
-      <x:c r="J79" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I79" s="10"/>
+      <x:c r="J79" s="10"/>
       <x:c r="K79" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L79" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M79"/>
-      <x:c r="N79"/>
-      <x:c r="O79"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M79" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N79" s="10"/>
+      <x:c r="O79" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="n">
@@ -3305,23 +3277,23 @@
       <x:c r="F80" s="10" t="str"/>
       <x:c r="G80" s="10" t="str"/>
       <x:c r="H80" s="10" t="str">
-        <x:v>ieee_saved_search_rss</x:v>
-      </x:c>
-      <x:c r="I80" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=7777658</x:v>
-      </x:c>
-      <x:c r="J80" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
-      </x:c>
+        <x:v>crossref_unified</x:v>
+      </x:c>
+      <x:c r="I80" s="10"/>
+      <x:c r="J80" s="10"/>
       <x:c r="K80" s="10" t="str">
-        <x:v>crossref-date-validation</x:v>
+        <x:v>crossref-pub+index</x:v>
       </x:c>
       <x:c r="L80" s="10" t="str">
-        <x:v>LOCAL V2: one shared IEEETrans15 Saved Search RSS is fetched once. The 15-journal whitelist removes Virtual Journals/Compendia; RSS timestamps remain discovery-only, with publisher/Crossref metadata used for the online date.</x:v>
-      </x:c>
-      <x:c r="M80"/>
-      <x:c r="N80"/>
-      <x:c r="O80"/>
+        <x:v>LOCAL V4: Crossref-only. Two-day member-level pub-date and index-date discovery; local ISSN/title whitelist; date priority published-online &gt; published &gt; issued &gt; published-print.</x:v>
+      </x:c>
+      <x:c r="M80" s="10" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="N80" s="10"/>
+      <x:c r="O80" s="10" t="str">
+        <x:v>IEEE-263</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
@@ -3361,101 +3333,101 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="str">
-        <x:v>IEEE Combined Saved Search RSS</x:v>
+        <x:v>Build</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>https://ieeexplore.ieee.org/search/searchresult.jsp?contentType=all&amp;sortType=newest&amp;filter=-ContentType+EQ+%22Newsletters%22&amp;matchBoolean=true&amp;rowsPerPage=10&amp;searchField=Search_All&amp;queryText=((PublicationTitle:%22IEEE+Transactions+on+Systems,+Man,+and+Cybernetics:+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Cybernetics%22OR+PublicationTitle:%22IEEE+Transactions+on+Computational+Social+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Fuzzy+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Reliability%22OR+PublicationTitle:%22IEEE+Transactions+on+Engineering+Management%22OR+PublicationTitle:%22IEEE+Transactions+on+Artificial+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Knowledge+and+Data+Engineering%22OR+PublicationTitle:%22IEEE+Transactions+on+Evolutionary+Computation%22OR+PublicationTitle:%22IEEE+Transactions+on+Neural+Networks+and+Learning+Systems%22OR+PublicationTitle:%22IEEE+Transactions+on+Pattern+Analysis+and+Machine+Intelligence%22OR+PublicationTitle:%22IEEE+Transactions+on+Big+Data%22OR+PublicationTitle:%22IEEE+Transactions+on+Network+Science+and+Engineering%22OR+PublicationTitle:%22IEEE/CAA+Journal+of+Automatica+Sinica%22OR+PublicationTitle:%22IEEE+Transactions+on+Emerging+Topics+in+Computational+Intelligence%22))&amp;searchOrigin=saved_searches&amp;rssFeed=true&amp;rssFeedName=IEEETrans15</x:v>
+        <x:v>LOCAL-2026.08.19-V4-CROSSREF</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>One feed covers all 15 IEEE journals. Duplicate URL values in Journals are deliberately fetched only once.</x:v>
+        <x:v>Unified Crossref-only collector.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="str">
-        <x:v>Elsevier strategy</x:v>
+        <x:v>Elsevier</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>Direct RSS (when configured) + Crossref index-date incremental discovery</x:v>
+        <x:v>Crossref member 78</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>ScienceDirect API/page scraping are disabled by default. Crossref-discovered records without published-online are retained as pending and rechecked.</x:v>
+        <x:v>39-journal local whitelist.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="str">
-        <x:v>Springer strategy</x:v>
+        <x:v>Springer Nature</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>Batch Meta API → per-journal Meta API → Online First → Crossref</x:v>
+        <x:v>Crossref member 297</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>A date-window Meta API query is attempted once and filtered locally to the 25-journal whitelist; onlineDate remains authoritative.</x:v>
+        <x:v>25-journal local whitelist.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="str">
-        <x:v>IEEE strategy</x:v>
+        <x:v>IEEE</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>Combined Saved Search RSS → publisher/Crossref date validation</x:v>
+        <x:v>Crossref member 263</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>The exact IEEETrans15 feed is preserved; RSS timestamps are discovery-only and Virtual Journals/Compendia are removed by the whitelist.</x:v>
+        <x:v>15-journal local whitelist.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
-        <x:v>LOCAL V3.3 build</x:v>
+        <x:v>Discovery pass 1</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>LOCAL-2026.08.19-V3.3</x:v>
+        <x:v>from-pub-date / until-pub-date</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>Optimized local-only collector.</x:v>
+        <x:v>Recent publication-date records.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
-        <x:v>Elsevier strategy</x:v>
+        <x:v>Discovery pass 2</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>Crossref member 78: online-date + publication-date</x:v>
+        <x:v>from-index-date / until-index-date</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>Two-day batch; no update-date scan.</x:v>
+        <x:v>Late metadata/re-index supplement.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
-        <x:v>IEEE strategy</x:v>
+        <x:v>Date priority</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>Combined Saved Search RSS + DOI/title Crossref matching</x:v>
+        <x:v>published-online &gt; published &gt; issued &gt; published-print</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>Whitelist matching by journal/ISSN; RSS pubDate is labelled fallback.</x:v>
+        <x:v>No publisher API/RSS/page dates.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
-        <x:v>Data quality</x:v>
+        <x:v>Window</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>Published status/date never downgraded by pending observations</x:v>
+        <x:v>2 calendar days</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>Higher-priority dates are protected.</x:v>
+        <x:v>Designed for daily local scheduling.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
-        <x:v>Daily window</x:v>
+        <x:v>Database</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>2 calendar dates</x:v>
+        <x:v>Fresh V4 database</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>Designed for daily Task Scheduler runs.</x:v>
+        <x:v>Previous V3 database intentionally reset on first V4 run.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3472,10 +3444,10 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="15" t="str">
+      <x:c r="A1" s="12" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="B1" s="15" t="str">
+      <x:c r="B1" s="12" t="str">
         <x:v>Instruction</x:v>
       </x:c>
     </x:row>
@@ -3484,7 +3456,7 @@
         <x:v>Enabled</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>1 = monitor/display; 0 = stop monitoring. Historical database rows are retained.</x:v>
+        <x:v>1 = monitor the journal; 0 = exclude it.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3492,79 +3464,79 @@
         <x:v>Mode</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>Elsevier uses elsevier_incremental; Springer uses springer_batch_api; IEEE uses ieee_saved_search_rss.</x:v>
+        <x:v>All enabled rows use crossref_unified in V4.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="str">
-        <x:v>Primary URL</x:v>
+        <x:v>Crossref Member</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>Retained as a human/reference publisher URL. ScienceDirect page scraping is disabled by default in LOCAL V2 after local HTTP 403 results.</x:v>
+        <x:v>Elsevier 78; Springer Nature 297; IEEE 263.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="str">
-        <x:v>RSS URL</x:v>
+        <x:v>Crossref Group</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>Elsevier: optional direct feed URL if you have a stable RSS address; blank is allowed. IEEE: all 15 rows intentionally share the same IEEETrans15 Saved Search RSS and it is fetched once.</x:v>
+        <x:v>Human-readable publisher/member grouping.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
-        <x:v>Fallback</x:v>
+        <x:v>Primary URL / RSS URL</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>Elsevier uses Crossref index-date incremental discovery + pending. Springer uses per-journal API/Online First/Crossref when the batch API path fails. IEEE uses publisher/Crossref date validation.</x:v>
+        <x:v>Not used by V4 and intentionally blank.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Fallback</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>Crossref items without published-online are saved as pending in SQLite and rechecked later; pending rows are never shown on the public page.</x:v>
+        <x:v>crossref-pub+index: pub-date discovery plus index-date supplement.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
-        <x:v>IEEE filtering</x:v>
+        <x:v>Whitelist matching</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>The crawler enforces the 15-journal whitelist, so Virtual Journals/Compendia are discarded unless underlying metadata resolves to a monitored journal.</x:v>
+        <x:v>ISSN/eISSN first; normalized Journal/Aliases second.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
-        <x:v>Date policy</x:v>
+        <x:v>Date priority</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>RSS pubDate is discovery time only. The displayed online date must come from Springer onlineDate, publisher metadata, or Crossref published-online.</x:v>
+        <x:v>published-online, then published, then issued, then published-print.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
-        <x:v>LOCAL V3.3 Elsevier</x:v>
+        <x:v>Daily run</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>Member 78 batch uses published-online first and generic publication-date second. It no longer scans all update-date metadata.</x:v>
+        <x:v>Use a two-day window so yesterday and today overlap across daily runs.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="10" t="str">
-        <x:v>Generic publication date</x:v>
+        <x:v>Database reset</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>Used only as a clearly labelled fallback when Crossref has no explicit published-online value.</x:v>
+        <x:v>V4 includes RESET_TO_V4.flag; first V4 sync deletes the old DB/JSON once.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="10" t="str">
-        <x:v>IEEE title matching</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>If the combined RSS does not expose journal/DOI metadata, the article title is searched in Crossref and accepted only if the result maps to one of the 15 IEEE whitelist journals.</x:v>
+        <x:v>Only CROSSREF_MAILTO is needed; no publisher API keys or RSS credentials.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
